--- a/sample/디지털.xlsx
+++ b/sample/디지털.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093634B6-6526-4493-A2E9-F25A51C93E8C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB94A96-D430-4CAF-9D83-66042BCED4EF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="견적서" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$L$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -1310,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1485,66 +1485,44 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1574,6 +1552,9 @@
     <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1581,6 +1562,7 @@
     <xf numFmtId="177" fontId="8" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1621,12 +1603,32 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1643,6 +1645,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1650,10 +1653,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1666,7 +1691,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1678,24 +1702,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2088,7 +2094,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L992"/>
+  <dimension ref="A1:L994"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="7.5703125" customWidth="1"/>
@@ -2107,14 +2113,14 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="112" t="s">
+      <c r="D1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="114"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="110"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2123,12 +2129,12 @@
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="96"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="90"/>
       <c r="J2" s="6"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2151,119 +2157,119 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4" s="111">
         <v>46225</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="117"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="113"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="118" t="s">
+      <c r="F4" s="114" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="122" t="s">
+      <c r="H4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="123"/>
+      <c r="I4" s="119"/>
       <c r="J4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="124" t="s">
+      <c r="K4" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="125"/>
+      <c r="L4" s="121"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="108"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="104"/>
       <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="119"/>
+      <c r="F5" s="115"/>
       <c r="G5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="104"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="99"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="108"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="120"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="77" t="s">
+      <c r="H6" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="106"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="101"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="135" t="str">
+      <c r="B7" s="137" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
-        <v>이백삼십오만오천칠백육십원정</v>
+        <v>일백오십팔만사천원정</v>
       </c>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="139"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="119"/>
+      <c r="F7" s="115"/>
       <c r="G7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="129" t="s">
+      <c r="H7" s="125" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="144"/>
+      <c r="I7" s="147"/>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="129" t="s">
+      <c r="K7" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="104"/>
+      <c r="L7" s="99"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="128"/>
-      <c r="B8" s="107">
+      <c r="A8" s="124"/>
+      <c r="B8" s="102">
         <f>I11</f>
-        <v>2355760</v>
+        <v>1584000</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="108"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="104"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="121"/>
+      <c r="F8" s="117"/>
       <c r="G8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="109" t="s">
+      <c r="H8" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="111"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="106"/>
+      <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="A9" s="19"/>
@@ -2283,18 +2289,18 @@
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="138" t="s">
+      <c r="B10" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="141"/>
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="140" t="s">
+      <c r="F10" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="141"/>
+      <c r="G10" s="143"/>
       <c r="H10" s="25" t="s">
         <v>21</v>
       </c>
@@ -2315,29 +2321,29 @@
       <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="109" t="str">
+      <c r="B11" s="105" t="str">
         <f>A5</f>
         <v xml:space="preserve"> 한국교육학술정보원</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
       <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="142" t="s">
+      <c r="F11" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="143"/>
+      <c r="G11" s="146"/>
       <c r="H11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="130">
-        <f>I41</f>
-        <v>2355760</v>
+      <c r="I11" s="159">
+        <f>I43</f>
+        <v>1584000</v>
       </c>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="93"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="87"/>
     </row>
     <row r="12" spans="1:12" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="21"/>
@@ -2354,56 +2360,56 @@
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="149" t="s">
+      <c r="A13" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="150"/>
-      <c r="C13" s="150"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="157" t="s">
+      <c r="B13" s="163"/>
+      <c r="C13" s="163"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="151"/>
-      <c r="G13" s="158" t="s">
+      <c r="F13" s="156"/>
+      <c r="G13" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="151"/>
-      <c r="I13" s="157" t="s">
+      <c r="H13" s="156"/>
+      <c r="I13" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="151"/>
-      <c r="K13" s="158" t="s">
+      <c r="J13" s="156"/>
+      <c r="K13" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="159"/>
+      <c r="L13" s="158"/>
     </row>
     <row r="14" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="66" t="s">
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="67"/>
+      <c r="F14" s="129"/>
       <c r="G14" s="53">
         <v>90</v>
       </c>
       <c r="H14" s="54">
         <v>40</v>
       </c>
-      <c r="I14" s="68">
+      <c r="I14" s="148">
         <f>SUM(I15:J18)</f>
-        <v>2141600</v>
+        <v>1440000</v>
       </c>
-      <c r="J14" s="69"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="71"/>
-    </row>
-    <row r="15" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="J14" s="149"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="153"/>
+    </row>
+    <row r="15" spans="1:12" ht="24.95" hidden="1" customHeight="1">
+      <c r="A15" s="130" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="32" t="s">
@@ -2412,51 +2418,50 @@
       <c r="C15" s="34"/>
       <c r="D15" s="33"/>
       <c r="E15" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="82">
         <v>300000</v>
       </c>
       <c r="H15" s="75"/>
-      <c r="I15" s="76">
+      <c r="I15" s="81">
         <f>G15*E15</f>
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J15" s="75"/>
-      <c r="K15" s="77"/>
+      <c r="K15" s="97"/>
       <c r="L15" s="78"/>
     </row>
-    <row r="16" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A16" s="146"/>
+    <row r="16" spans="1:12" ht="24.95" hidden="1" customHeight="1">
+      <c r="A16" s="131"/>
       <c r="B16" s="32" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="34"/>
       <c r="D16" s="33"/>
       <c r="E16" s="35">
-        <f>H14</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="74">
+      <c r="G16" s="82">
         <v>10040</v>
       </c>
       <c r="H16" s="75"/>
-      <c r="I16" s="76">
+      <c r="I16" s="81">
         <f>G16*E16</f>
-        <v>401600</v>
+        <v>0</v>
       </c>
       <c r="J16" s="75"/>
-      <c r="K16" s="77"/>
+      <c r="K16" s="97"/>
       <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="152" t="s">
+      <c r="A17" s="164" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="32" t="s">
@@ -2472,20 +2477,20 @@
       <c r="F17" s="38">
         <v>90</v>
       </c>
-      <c r="G17" s="74">
+      <c r="G17" s="82">
         <v>300</v>
       </c>
       <c r="H17" s="75"/>
-      <c r="I17" s="76">
+      <c r="I17" s="81">
         <f>E17*F17*G17</f>
         <v>1080000</v>
       </c>
       <c r="J17" s="75"/>
-      <c r="K17" s="77"/>
+      <c r="K17" s="97"/>
       <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="153"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="34" t="s">
         <v>59</v>
       </c>
@@ -2497,47 +2502,47 @@
       <c r="F18" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="74">
+      <c r="G18" s="82">
         <v>4000</v>
       </c>
       <c r="H18" s="75"/>
-      <c r="I18" s="76">
+      <c r="I18" s="81">
         <f>G18*E18</f>
         <v>360000</v>
       </c>
       <c r="J18" s="75"/>
-      <c r="K18" s="77" t="s">
+      <c r="K18" s="97" t="s">
         <v>60</v>
       </c>
       <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="66" t="s">
+      <c r="B19" s="127"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="67"/>
+      <c r="F19" s="129"/>
       <c r="G19" s="52">
         <v>0</v>
       </c>
       <c r="H19" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="68">
+      <c r="I19" s="148">
         <f>SUM(I20:J21)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="69"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="71"/>
+      <c r="J19" s="149"/>
+      <c r="K19" s="150"/>
+      <c r="L19" s="153"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="132" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -2551,20 +2556,20 @@
       <c r="F20" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="74">
+      <c r="G20" s="82">
         <v>60000</v>
       </c>
       <c r="H20" s="75"/>
-      <c r="I20" s="76">
+      <c r="I20" s="81">
         <f t="shared" ref="I20:I21" si="0">G20*E20</f>
         <v>0</v>
       </c>
       <c r="J20" s="75"/>
-      <c r="K20" s="77"/>
+      <c r="K20" s="97"/>
       <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="73"/>
+      <c r="A21" s="133"/>
       <c r="B21" s="47" t="s">
         <v>55</v>
       </c>
@@ -2577,47 +2582,47 @@
       <c r="F21" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="79">
+      <c r="G21" s="134">
         <v>60000</v>
       </c>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81">
+      <c r="H21" s="135"/>
+      <c r="I21" s="154">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="80"/>
-      <c r="K21" s="165" t="s">
+      <c r="J21" s="135"/>
+      <c r="K21" s="169" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="166"/>
+      <c r="L21" s="170"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="66" t="s">
+      <c r="B22" s="127"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="128" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="67"/>
+      <c r="F22" s="129"/>
       <c r="G22" s="52">
         <v>0</v>
       </c>
       <c r="H22" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="68">
+      <c r="I22" s="148">
         <f>SUM(I23:J24)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="69"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="71"/>
+      <c r="J22" s="149"/>
+      <c r="K22" s="150"/>
+      <c r="L22" s="153"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="132" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="32" t="s">
@@ -2631,20 +2636,20 @@
       <c r="F23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="74">
+      <c r="G23" s="82">
         <v>60000</v>
       </c>
       <c r="H23" s="75"/>
-      <c r="I23" s="76">
+      <c r="I23" s="81">
         <f>G23*E23</f>
         <v>0</v>
       </c>
       <c r="J23" s="75"/>
-      <c r="K23" s="77"/>
+      <c r="K23" s="97"/>
       <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A24" s="73"/>
+      <c r="A24" s="133"/>
       <c r="B24" s="47" t="s">
         <v>32</v>
       </c>
@@ -2657,43 +2662,43 @@
       <c r="F24" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="79">
+      <c r="G24" s="134">
         <v>50000</v>
       </c>
-      <c r="H24" s="80"/>
-      <c r="I24" s="81">
+      <c r="H24" s="135"/>
+      <c r="I24" s="154">
         <f>G24*E24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="80"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="83"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="72"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="67"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="129"/>
       <c r="G25" s="56">
         <v>0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="68">
+      <c r="I25" s="148">
         <f>SUM(I26:J27)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="133"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="132"/>
+      <c r="J25" s="152"/>
+      <c r="K25" s="150"/>
+      <c r="L25" s="151"/>
     </row>
     <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="132" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="32" t="s">
@@ -2707,20 +2712,20 @@
       <c r="F26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="74">
+      <c r="G26" s="82">
         <v>50000</v>
       </c>
       <c r="H26" s="75"/>
-      <c r="I26" s="76">
+      <c r="I26" s="81">
         <f t="shared" ref="I26" si="1">G26*E26</f>
         <v>0</v>
       </c>
       <c r="J26" s="75"/>
-      <c r="K26" s="77"/>
+      <c r="K26" s="97"/>
       <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A27" s="156"/>
+      <c r="A27" s="168"/>
       <c r="B27" s="32" t="s">
         <v>35</v>
       </c>
@@ -2733,28 +2738,28 @@
       <c r="F27" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="74">
+      <c r="G27" s="82">
         <v>4500</v>
       </c>
       <c r="H27" s="75"/>
-      <c r="I27" s="76">
+      <c r="I27" s="81">
         <f>G27*E27</f>
         <v>0</v>
       </c>
       <c r="J27" s="75"/>
-      <c r="K27" s="163" t="s">
+      <c r="K27" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="164"/>
+      <c r="L27" s="80"/>
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A28" s="160"/>
+      <c r="A28" s="64"/>
       <c r="B28" s="32"/>
       <c r="C28" s="34"/>
       <c r="D28" s="33"/>
       <c r="E28" s="60"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="162"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="66"/>
       <c r="H28" s="63"/>
       <c r="I28" s="62"/>
       <c r="J28" s="59"/>
@@ -2762,13 +2767,13 @@
       <c r="L28" s="58"/>
     </row>
     <row r="29" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A29" s="160"/>
+      <c r="A29" s="64"/>
       <c r="B29" s="32"/>
       <c r="C29" s="34"/>
       <c r="D29" s="33"/>
       <c r="E29" s="60"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="162"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="66"/>
       <c r="H29" s="63"/>
       <c r="I29" s="62"/>
       <c r="J29" s="59"/>
@@ -2776,13 +2781,13 @@
       <c r="L29" s="58"/>
     </row>
     <row r="30" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A30" s="160"/>
+      <c r="A30" s="64"/>
       <c r="B30" s="32"/>
       <c r="C30" s="34"/>
       <c r="D30" s="33"/>
       <c r="E30" s="60"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="162"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="66"/>
       <c r="H30" s="63"/>
       <c r="I30" s="62"/>
       <c r="J30" s="59"/>
@@ -2790,13 +2795,13 @@
       <c r="L30" s="58"/>
     </row>
     <row r="31" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A31" s="160"/>
+      <c r="A31" s="64"/>
       <c r="B31" s="32"/>
       <c r="C31" s="34"/>
       <c r="D31" s="33"/>
       <c r="E31" s="60"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="162"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="66"/>
       <c r="H31" s="63"/>
       <c r="I31" s="62"/>
       <c r="J31" s="59"/>
@@ -2804,13 +2809,13 @@
       <c r="L31" s="58"/>
     </row>
     <row r="32" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A32" s="160"/>
+      <c r="A32" s="64"/>
       <c r="B32" s="32"/>
       <c r="C32" s="34"/>
       <c r="D32" s="33"/>
       <c r="E32" s="60"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="162"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="66"/>
       <c r="H32" s="63"/>
       <c r="I32" s="62"/>
       <c r="J32" s="59"/>
@@ -2818,13 +2823,13 @@
       <c r="L32" s="58"/>
     </row>
     <row r="33" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A33" s="160"/>
+      <c r="A33" s="64"/>
       <c r="B33" s="32"/>
       <c r="C33" s="34"/>
       <c r="D33" s="33"/>
       <c r="E33" s="60"/>
-      <c r="F33" s="161"/>
-      <c r="G33" s="162"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="66"/>
       <c r="H33" s="63"/>
       <c r="I33" s="62"/>
       <c r="J33" s="59"/>
@@ -2832,13 +2837,13 @@
       <c r="L33" s="58"/>
     </row>
     <row r="34" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A34" s="160"/>
+      <c r="A34" s="64"/>
       <c r="B34" s="32"/>
       <c r="C34" s="34"/>
       <c r="D34" s="33"/>
       <c r="E34" s="60"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="162"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="66"/>
       <c r="H34" s="63"/>
       <c r="I34" s="62"/>
       <c r="J34" s="59"/>
@@ -2846,13 +2851,13 @@
       <c r="L34" s="58"/>
     </row>
     <row r="35" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A35" s="160"/>
+      <c r="A35" s="64"/>
       <c r="B35" s="32"/>
       <c r="C35" s="34"/>
       <c r="D35" s="33"/>
       <c r="E35" s="60"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="162"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="66"/>
       <c r="H35" s="63"/>
       <c r="I35" s="62"/>
       <c r="J35" s="59"/>
@@ -2860,13 +2865,13 @@
       <c r="L35" s="58"/>
     </row>
     <row r="36" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A36" s="160"/>
+      <c r="A36" s="64"/>
       <c r="B36" s="32"/>
       <c r="C36" s="34"/>
       <c r="D36" s="33"/>
       <c r="E36" s="60"/>
-      <c r="F36" s="161"/>
-      <c r="G36" s="162"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="66"/>
       <c r="H36" s="63"/>
       <c r="I36" s="62"/>
       <c r="J36" s="59"/>
@@ -2874,136 +2879,136 @@
       <c r="L36" s="58"/>
     </row>
     <row r="37" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A37" s="160"/>
+      <c r="A37" s="64"/>
       <c r="B37" s="32"/>
       <c r="C37" s="34"/>
       <c r="D37" s="33"/>
       <c r="E37" s="60"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="59"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="68"/>
       <c r="K37" s="61"/>
-      <c r="L37" s="58"/>
-    </row>
-    <row r="38" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A38" s="154" t="s">
+      <c r="L37" s="67"/>
+    </row>
+    <row r="38" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A38" s="64"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="67"/>
+    </row>
+    <row r="39" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A39" s="64"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="58"/>
+    </row>
+    <row r="40" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A40" s="166" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="84">
+      <c r="B40" s="74"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="76">
         <f>SUM(I14,I22,I19,I25)</f>
-        <v>2141600</v>
+        <v>1440000</v>
       </c>
-      <c r="J38" s="75"/>
-      <c r="K38" s="88"/>
-      <c r="L38" s="78"/>
-    </row>
-    <row r="39" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A39" s="155" t="s">
+      <c r="J40" s="75"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="78"/>
+    </row>
+    <row r="41" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A41" s="167" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="139"/>
-      <c r="C39" s="139"/>
-      <c r="D39" s="98"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="97">
-        <f>I38</f>
-        <v>2141600</v>
+      <c r="B41" s="141"/>
+      <c r="C41" s="141"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="91">
+        <f>I40</f>
+        <v>1440000</v>
       </c>
-      <c r="J39" s="98"/>
-      <c r="K39" s="99"/>
-      <c r="L39" s="100"/>
-    </row>
-    <row r="40" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A40" s="147" t="s">
+      <c r="J41" s="92"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="94"/>
+    </row>
+    <row r="42" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A42" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="101"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="102">
-        <f>I39*0.1</f>
-        <v>214160</v>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="96">
+        <f>I41*0.1</f>
+        <v>144000</v>
       </c>
-      <c r="J40" s="75"/>
-      <c r="K40" s="88"/>
-      <c r="L40" s="78"/>
-    </row>
-    <row r="41" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A41" s="148" t="s">
+      <c r="J42" s="75"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="78"/>
+    </row>
+    <row r="43" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A43" s="161" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="131"/>
-      <c r="C41" s="131"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="91">
-        <f>ROUND(SUM(I39:J40),0)</f>
-        <v>2355760</v>
+      <c r="B43" s="144"/>
+      <c r="C43" s="144"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="85">
+        <f>ROUND(SUM(I41:J42),0)</f>
+        <v>1584000</v>
       </c>
-      <c r="J41" s="90"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="93"/>
-    </row>
-    <row r="42" spans="1:12" ht="13.5">
-      <c r="A42" s="94"/>
-      <c r="B42" s="95"/>
-      <c r="C42" s="95"/>
-      <c r="D42" s="95"/>
-      <c r="E42" s="95"/>
-      <c r="F42" s="95"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
-      <c r="I42" s="95"/>
-      <c r="J42" s="95"/>
-      <c r="K42" s="95"/>
-      <c r="L42" s="96"/>
-    </row>
-    <row r="43" spans="1:12" ht="13.5">
-      <c r="A43" s="46"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="87"/>
     </row>
     <row r="44" spans="1:12" ht="13.5">
-      <c r="A44" s="46"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
+      <c r="A44" s="88"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
+      <c r="L44" s="90"/>
     </row>
     <row r="45" spans="1:12" ht="13.5">
       <c r="A45" s="46"/>
@@ -3027,8 +3032,8 @@
       <c r="E46" s="46"/>
       <c r="F46" s="46"/>
       <c r="G46" s="46"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
       <c r="J46" s="46"/>
       <c r="K46" s="46"/>
       <c r="L46" s="46"/>
@@ -3055,9 +3060,9 @@
       <c r="E48" s="46"/>
       <c r="F48" s="46"/>
       <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="46"/>
       <c r="K48" s="46"/>
       <c r="L48" s="46"/>
     </row>
@@ -3113,7 +3118,7 @@
       <c r="G52" s="46"/>
       <c r="H52" s="46"/>
       <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
+      <c r="J52" s="45"/>
       <c r="K52" s="46"/>
       <c r="L52" s="46"/>
     </row>
@@ -16277,35 +16282,64 @@
       <c r="K992" s="46"/>
       <c r="L992" s="46"/>
     </row>
+    <row r="993" spans="1:12" ht="13.5">
+      <c r="A993" s="46"/>
+      <c r="B993" s="46"/>
+      <c r="C993" s="46"/>
+      <c r="D993" s="46"/>
+      <c r="E993" s="46"/>
+      <c r="F993" s="46"/>
+      <c r="G993" s="46"/>
+      <c r="H993" s="46"/>
+      <c r="I993" s="46"/>
+      <c r="J993" s="46"/>
+      <c r="K993" s="46"/>
+      <c r="L993" s="46"/>
+    </row>
+    <row r="994" spans="1:12" ht="13.5">
+      <c r="A994" s="46"/>
+      <c r="B994" s="46"/>
+      <c r="C994" s="46"/>
+      <c r="D994" s="46"/>
+      <c r="E994" s="46"/>
+      <c r="F994" s="46"/>
+      <c r="G994" s="46"/>
+      <c r="H994" s="46"/>
+      <c r="I994" s="46"/>
+      <c r="J994" s="46"/>
+      <c r="K994" s="46"/>
+      <c r="L994" s="46"/>
+    </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="I11:L11"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B7:D7"/>
@@ -16314,15 +16348,27 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
     <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="H6:L6"/>
     <mergeCell ref="B8:D8"/>
@@ -16335,42 +16381,29 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:L44"/>
     <mergeCell ref="I41:J41"/>
     <mergeCell ref="K41:L41"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="E40:H40"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:L40"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I25:J25"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/sample/디지털.xlsx
+++ b/sample/디지털.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB94A96-D430-4CAF-9D83-66042BCED4EF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30637C8B-E293-4884-AA08-299DAE8885F0}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t xml:space="preserve">  견   적   서</t>
   </si>
@@ -241,6 +241,10 @@
     <t>사단법인 아름다운사람들</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>무선제본</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -265,6 +269,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -429,7 +434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="72">
+  <borders count="75">
     <border>
       <left/>
       <right/>
@@ -1306,11 +1311,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1498,61 +1546,124 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1562,11 +1673,6 @@
     <xf numFmtId="177" fontId="8" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1574,6 +1680,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1600,86 +1708,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1687,25 +1741,37 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2113,14 +2179,14 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="110"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="134"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2129,12 +2195,12 @@
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="90"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="136"/>
       <c r="J2" s="6"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2157,119 +2223,119 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="111">
+      <c r="B4" s="137">
         <v>46225</v>
       </c>
-      <c r="C4" s="112"/>
-      <c r="D4" s="113"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="139"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="114" t="s">
+      <c r="F4" s="140" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="118" t="s">
+      <c r="H4" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="119"/>
+      <c r="I4" s="145"/>
       <c r="J4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="120" t="s">
+      <c r="K4" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="121"/>
+      <c r="L4" s="147"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="148" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="104"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="115"/>
+      <c r="F5" s="141"/>
       <c r="G5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="97" t="s">
+      <c r="H5" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="99"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="126"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1">
-      <c r="A6" s="136" t="s">
+      <c r="A6" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="116"/>
+      <c r="F6" s="142"/>
       <c r="G6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="97" t="s">
+      <c r="H6" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="101"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="128"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="A7" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="137" t="str">
+      <c r="B7" s="106" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
         <v>일백오십팔만사천원정</v>
       </c>
-      <c r="C7" s="138"/>
-      <c r="D7" s="139"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="115"/>
+      <c r="F7" s="141"/>
       <c r="G7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="125" t="s">
+      <c r="H7" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="147"/>
+      <c r="I7" s="116"/>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="125" t="s">
+      <c r="K7" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="99"/>
+      <c r="L7" s="126"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="124"/>
-      <c r="B8" s="102">
+      <c r="A8" s="150"/>
+      <c r="B8" s="129">
         <f>I11</f>
         <v>1584000</v>
       </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="105"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="117"/>
+      <c r="F8" s="143"/>
       <c r="G8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="105" t="s">
+      <c r="H8" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="107"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="A9" s="19"/>
@@ -2289,18 +2355,18 @@
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="140" t="s">
+      <c r="B10" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="142" t="s">
+      <c r="F10" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="143"/>
+      <c r="G10" s="111"/>
       <c r="H10" s="25" t="s">
         <v>21</v>
       </c>
@@ -2321,29 +2387,29 @@
       <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="105" t="str">
+      <c r="B11" s="112" t="str">
         <f>A5</f>
         <v xml:space="preserve"> 한국교육학술정보원</v>
       </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
       <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="145" t="s">
+      <c r="F11" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="146"/>
+      <c r="G11" s="114"/>
       <c r="H11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="159">
+      <c r="I11" s="95">
         <f>I43</f>
         <v>1584000</v>
       </c>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="87"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="97"/>
     </row>
     <row r="12" spans="1:12" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="21"/>
@@ -2360,56 +2426,56 @@
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="162" t="s">
+      <c r="A13" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="163"/>
-      <c r="C13" s="163"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="155" t="s">
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="156"/>
-      <c r="G13" s="157" t="s">
+      <c r="F13" s="78"/>
+      <c r="G13" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="156"/>
-      <c r="I13" s="155" t="s">
+      <c r="H13" s="78"/>
+      <c r="I13" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="156"/>
-      <c r="K13" s="157" t="s">
+      <c r="J13" s="78"/>
+      <c r="K13" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="158"/>
+      <c r="L13" s="91"/>
     </row>
     <row r="14" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="128" t="s">
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="129"/>
+      <c r="F14" s="122"/>
       <c r="G14" s="53">
         <v>90</v>
       </c>
       <c r="H14" s="54">
         <v>40</v>
       </c>
-      <c r="I14" s="148">
+      <c r="I14" s="100">
         <f>SUM(I15:J18)</f>
         <v>1440000</v>
       </c>
-      <c r="J14" s="149"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="153"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="99"/>
     </row>
     <row r="15" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="123" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="32" t="s">
@@ -2423,20 +2489,20 @@
       <c r="F15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="82">
+      <c r="G15" s="102">
         <v>300000</v>
       </c>
-      <c r="H15" s="75"/>
-      <c r="I15" s="81">
+      <c r="H15" s="82"/>
+      <c r="I15" s="94">
         <f>G15*E15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="75"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="78"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="93"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A16" s="131"/>
+      <c r="A16" s="124"/>
       <c r="B16" s="32" t="s">
         <v>16</v>
       </c>
@@ -2448,20 +2514,20 @@
       <c r="F16" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="102">
         <v>10040</v>
       </c>
-      <c r="H16" s="75"/>
-      <c r="I16" s="81">
+      <c r="H16" s="82"/>
+      <c r="I16" s="94">
         <f>G16*E16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="75"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="78"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="93"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="164" t="s">
+      <c r="A17" s="119" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="32" t="s">
@@ -2477,99 +2543,101 @@
       <c r="F17" s="38">
         <v>90</v>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="102">
         <v>300</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="81">
+      <c r="H17" s="82"/>
+      <c r="I17" s="94">
         <f>E17*F17*G17</f>
         <v>1080000</v>
       </c>
-      <c r="J17" s="75"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="78"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="93"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="165"/>
+      <c r="A18" s="120"/>
       <c r="B18" s="34" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="34"/>
-      <c r="D18" s="33"/>
+      <c r="D18" s="33" t="s">
+        <v>63</v>
+      </c>
       <c r="E18" s="35">
         <v>90</v>
       </c>
       <c r="F18" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="82">
+      <c r="G18" s="102">
         <v>4000</v>
       </c>
-      <c r="H18" s="75"/>
-      <c r="I18" s="81">
+      <c r="H18" s="82"/>
+      <c r="I18" s="94">
         <f>G18*E18</f>
         <v>360000</v>
       </c>
-      <c r="J18" s="75"/>
-      <c r="K18" s="97" t="s">
+      <c r="J18" s="82"/>
+      <c r="K18" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="78"/>
+      <c r="L18" s="93"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A19" s="126" t="s">
+      <c r="A19" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="127"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="128" t="s">
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="129"/>
+      <c r="F19" s="122"/>
       <c r="G19" s="52">
         <v>0</v>
       </c>
       <c r="H19" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="148">
+      <c r="I19" s="100">
         <f>SUM(I20:J21)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="149"/>
-      <c r="K19" s="150"/>
-      <c r="L19" s="153"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="99"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="172" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="173" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="35">
+      <c r="C20" s="174"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="71">
         <v>0</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="176" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="82">
+      <c r="G20" s="102">
         <v>60000</v>
       </c>
-      <c r="H20" s="75"/>
-      <c r="I20" s="81">
+      <c r="H20" s="82"/>
+      <c r="I20" s="94">
         <f t="shared" ref="I20:I21" si="0">G20*E20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="75"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="78"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="93"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="133"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="47" t="s">
         <v>55</v>
       </c>
@@ -2582,47 +2650,47 @@
       <c r="F21" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="134">
+      <c r="G21" s="76">
         <v>60000</v>
       </c>
-      <c r="H21" s="135"/>
-      <c r="I21" s="154">
+      <c r="H21" s="75"/>
+      <c r="I21" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="135"/>
-      <c r="K21" s="169" t="s">
+      <c r="J21" s="75"/>
+      <c r="K21" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="170"/>
+      <c r="L21" s="73"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="127"/>
-      <c r="C22" s="127"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="128" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="129"/>
+      <c r="F22" s="122"/>
       <c r="G22" s="52">
         <v>0</v>
       </c>
       <c r="H22" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="148">
+      <c r="I22" s="100">
         <f>SUM(I23:J24)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="149"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="153"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="98"/>
+      <c r="L22" s="99"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="86" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="32" t="s">
@@ -2630,26 +2698,26 @@
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="33"/>
-      <c r="E23" s="35">
+      <c r="E23" s="60">
         <v>0</v>
       </c>
       <c r="F23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="102">
         <v>60000</v>
       </c>
-      <c r="H23" s="75"/>
-      <c r="I23" s="81">
+      <c r="H23" s="82"/>
+      <c r="I23" s="94">
         <f>G23*E23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="75"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="78"/>
+      <c r="J23" s="82"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="93"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A24" s="133"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="47" t="s">
         <v>32</v>
       </c>
@@ -2662,43 +2730,43 @@
       <c r="F24" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="134">
+      <c r="G24" s="76">
         <v>50000</v>
       </c>
-      <c r="H24" s="135"/>
-      <c r="I24" s="154">
+      <c r="H24" s="75"/>
+      <c r="I24" s="74">
         <f>G24*E24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="135"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="72"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="165"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A25" s="126" t="s">
+      <c r="A25" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="129"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="122"/>
       <c r="G25" s="56">
         <v>0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="148">
+      <c r="I25" s="100">
         <f>SUM(I26:J27)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="152"/>
-      <c r="K25" s="150"/>
-      <c r="L25" s="151"/>
+      <c r="J25" s="171"/>
+      <c r="K25" s="98"/>
+      <c r="L25" s="170"/>
     </row>
     <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A26" s="132" t="s">
+      <c r="A26" s="86" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="32" t="s">
@@ -2706,51 +2774,51 @@
       </c>
       <c r="C26" s="34"/>
       <c r="D26" s="33"/>
-      <c r="E26" s="35">
+      <c r="E26" s="60">
         <v>0</v>
       </c>
       <c r="F26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="82">
+      <c r="G26" s="102">
         <v>50000</v>
       </c>
-      <c r="H26" s="75"/>
-      <c r="I26" s="81">
+      <c r="H26" s="82"/>
+      <c r="I26" s="94">
         <f t="shared" ref="I26" si="1">G26*E26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="75"/>
-      <c r="K26" s="97"/>
-      <c r="L26" s="78"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="93"/>
     </row>
     <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A27" s="168"/>
+      <c r="A27" s="87"/>
       <c r="B27" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="34"/>
       <c r="D27" s="33"/>
-      <c r="E27" s="35">
+      <c r="E27" s="60">
         <f>G25</f>
         <v>0</v>
       </c>
       <c r="F27" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="82">
+      <c r="G27" s="102">
         <v>4500</v>
       </c>
-      <c r="H27" s="75"/>
-      <c r="I27" s="81">
+      <c r="H27" s="82"/>
+      <c r="I27" s="94">
         <f>G27*E27</f>
         <v>0</v>
       </c>
-      <c r="J27" s="75"/>
-      <c r="K27" s="79" t="s">
+      <c r="J27" s="82"/>
+      <c r="K27" s="168" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="80"/>
+      <c r="L27" s="169"/>
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1">
       <c r="A28" s="64"/>
@@ -2921,94 +2989,94 @@
       <c r="L39" s="58"/>
     </row>
     <row r="40" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A40" s="166" t="s">
+      <c r="A40" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="74"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="76">
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="167">
         <f>SUM(I14,I22,I19,I25)</f>
         <v>1440000</v>
       </c>
-      <c r="J40" s="75"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="78"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="93"/>
     </row>
     <row r="41" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A41" s="167" t="s">
+      <c r="A41" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="141"/>
-      <c r="D41" s="92"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="85"/>
       <c r="E41" s="39"/>
       <c r="F41" s="40"/>
       <c r="G41" s="41"/>
       <c r="H41" s="42"/>
-      <c r="I41" s="91">
+      <c r="I41" s="156">
         <f>I40</f>
         <v>1440000</v>
       </c>
-      <c r="J41" s="92"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="94"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="157"/>
+      <c r="L41" s="158"/>
     </row>
     <row r="42" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A42" s="160" t="s">
+      <c r="A42" s="162" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="75"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="82"/>
       <c r="E42" s="43"/>
       <c r="F42" s="43"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="96">
+      <c r="G42" s="159"/>
+      <c r="H42" s="82"/>
+      <c r="I42" s="160">
         <f>I41*0.1</f>
         <v>144000</v>
       </c>
-      <c r="J42" s="75"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="161"/>
+      <c r="L42" s="93"/>
     </row>
     <row r="43" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A43" s="161" t="s">
+      <c r="A43" s="163" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="144"/>
-      <c r="C43" s="144"/>
-      <c r="D43" s="84"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="152"/>
       <c r="E43" s="44"/>
       <c r="F43" s="44"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="85">
+      <c r="G43" s="151"/>
+      <c r="H43" s="152"/>
+      <c r="I43" s="153">
         <f>ROUND(SUM(I41:J42),0)</f>
         <v>1584000</v>
       </c>
-      <c r="J43" s="84"/>
-      <c r="K43" s="86"/>
-      <c r="L43" s="87"/>
+      <c r="J43" s="152"/>
+      <c r="K43" s="154"/>
+      <c r="L43" s="97"/>
     </row>
     <row r="44" spans="1:12" ht="13.5">
-      <c r="A44" s="88"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="89"/>
-      <c r="D44" s="89"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="89"/>
-      <c r="H44" s="89"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="89"/>
-      <c r="K44" s="89"/>
-      <c r="L44" s="90"/>
+      <c r="A44" s="155"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="135"/>
+      <c r="D44" s="135"/>
+      <c r="E44" s="135"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="135"/>
+      <c r="H44" s="135"/>
+      <c r="I44" s="135"/>
+      <c r="J44" s="135"/>
+      <c r="K44" s="135"/>
+      <c r="L44" s="136"/>
     </row>
     <row r="45" spans="1:12" ht="13.5">
       <c r="A45" s="46"/>
@@ -16312,63 +16380,28 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="H6:L6"/>
     <mergeCell ref="B8:D8"/>
@@ -16381,29 +16414,64 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="K24:L24"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G17:H17"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/sample/디지털.xlsx
+++ b/sample/디지털.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30637C8B-E293-4884-AA08-299DAE8885F0}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409C9C21-4C48-4738-9DF4-80E4A50D9A4E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24480" yWindow="1092" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="2" r:id="rId1"/>
@@ -1549,46 +1549,22 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1596,82 +1572,74 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="8" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1680,8 +1648,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1708,70 +1674,104 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2179,14 +2179,14 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="132" t="s">
+      <c r="D1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="134"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="120"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2195,12 +2195,12 @@
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="136"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="6"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2223,119 +2223,119 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="137">
+      <c r="B4" s="121">
         <v>46225</v>
       </c>
-      <c r="C4" s="138"/>
-      <c r="D4" s="139"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="123"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="140" t="s">
+      <c r="F4" s="124" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="144" t="s">
+      <c r="H4" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="145"/>
+      <c r="I4" s="129"/>
       <c r="J4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="146" t="s">
+      <c r="K4" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="147"/>
+      <c r="L4" s="131"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="105"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="114"/>
       <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="141"/>
+      <c r="F5" s="125"/>
       <c r="G5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="126"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="109"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="114"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="142"/>
+      <c r="F6" s="126"/>
       <c r="G6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="92" t="s">
+      <c r="H6" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="128"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="111"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="149" t="s">
+      <c r="A7" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="106" t="str">
+      <c r="B7" s="155" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
         <v>일백오십팔만사천원정</v>
       </c>
-      <c r="C7" s="107"/>
-      <c r="D7" s="108"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="157"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="141"/>
+      <c r="F7" s="125"/>
       <c r="G7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="115" t="s">
+      <c r="H7" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="116"/>
+      <c r="I7" s="151"/>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="115" t="s">
+      <c r="K7" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="126"/>
+      <c r="L7" s="109"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="150"/>
-      <c r="B8" s="129">
+      <c r="A8" s="134"/>
+      <c r="B8" s="112">
         <f>I11</f>
         <v>1584000</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="114"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="143"/>
+      <c r="F8" s="127"/>
       <c r="G8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="112" t="s">
+      <c r="H8" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="131"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="116"/>
+      <c r="L8" s="117"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="A9" s="19"/>
@@ -2355,18 +2355,18 @@
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="109" t="s">
+      <c r="B10" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="159"/>
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="110" t="s">
+      <c r="F10" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="111"/>
+      <c r="G10" s="161"/>
       <c r="H10" s="25" t="s">
         <v>21</v>
       </c>
@@ -2387,29 +2387,29 @@
       <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="112" t="str">
+      <c r="B11" s="115" t="str">
         <f>A5</f>
         <v xml:space="preserve"> 한국교육학술정보원</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
       <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="113" t="s">
+      <c r="F11" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="114"/>
+      <c r="G11" s="163"/>
       <c r="H11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="95">
+      <c r="I11" s="168">
         <f>I43</f>
         <v>1584000</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="97"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="95"/>
     </row>
     <row r="12" spans="1:12" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="21"/>
@@ -2426,56 +2426,56 @@
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="117" t="s">
+      <c r="A13" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="77" t="s">
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79" t="s">
+      <c r="F13" s="146"/>
+      <c r="G13" s="175" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="77" t="s">
+      <c r="H13" s="146"/>
+      <c r="I13" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="78"/>
-      <c r="K13" s="79" t="s">
+      <c r="J13" s="146"/>
+      <c r="K13" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="91"/>
+      <c r="L13" s="176"/>
     </row>
     <row r="14" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="121" t="s">
+      <c r="B14" s="139"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="122"/>
+      <c r="F14" s="137"/>
       <c r="G14" s="53">
         <v>90</v>
       </c>
       <c r="H14" s="54">
         <v>40</v>
       </c>
-      <c r="I14" s="100">
+      <c r="I14" s="83">
         <f>SUM(I15:J18)</f>
         <v>1440000</v>
       </c>
-      <c r="J14" s="101"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="99"/>
+      <c r="J14" s="152"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="165"/>
     </row>
     <row r="15" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="149" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="32" t="s">
@@ -2489,20 +2489,20 @@
       <c r="F15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="102">
+      <c r="G15" s="76">
         <v>300000</v>
       </c>
-      <c r="H15" s="82"/>
-      <c r="I15" s="94">
+      <c r="H15" s="77"/>
+      <c r="I15" s="80">
         <f>G15*E15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="82"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="93"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="79"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A16" s="124"/>
+      <c r="A16" s="150"/>
       <c r="B16" s="32" t="s">
         <v>16</v>
       </c>
@@ -2514,20 +2514,20 @@
       <c r="F16" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="102">
+      <c r="G16" s="76">
         <v>10040</v>
       </c>
-      <c r="H16" s="82"/>
-      <c r="I16" s="94">
+      <c r="H16" s="77"/>
+      <c r="I16" s="80">
         <f>G16*E16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="82"/>
-      <c r="K16" s="92"/>
-      <c r="L16" s="93"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="147" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="32" t="s">
@@ -2543,20 +2543,20 @@
       <c r="F17" s="38">
         <v>90</v>
       </c>
-      <c r="G17" s="102">
+      <c r="G17" s="76">
         <v>300</v>
       </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="94">
+      <c r="H17" s="77"/>
+      <c r="I17" s="80">
         <f>E17*F17*G17</f>
         <v>1080000</v>
       </c>
-      <c r="J17" s="82"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="93"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="79"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="120"/>
+      <c r="A18" s="148"/>
       <c r="B18" s="34" t="s">
         <v>59</v>
       </c>
@@ -2570,74 +2570,74 @@
       <c r="F18" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="102">
+      <c r="G18" s="76">
         <v>4000</v>
       </c>
-      <c r="H18" s="82"/>
-      <c r="I18" s="94">
+      <c r="H18" s="77"/>
+      <c r="I18" s="80">
         <f>G18*E18</f>
         <v>360000</v>
       </c>
-      <c r="J18" s="82"/>
-      <c r="K18" s="92" t="s">
+      <c r="J18" s="77"/>
+      <c r="K18" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="93"/>
+      <c r="L18" s="79"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="138" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="121" t="s">
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="136" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="122"/>
+      <c r="F19" s="137"/>
       <c r="G19" s="52">
         <v>0</v>
       </c>
       <c r="H19" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="100">
+      <c r="I19" s="83">
         <f>SUM(I20:J21)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="101"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="99"/>
+      <c r="J19" s="152"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="165"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1">
       <c r="A20" s="172" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="173" t="s">
+      <c r="B20" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="174"/>
-      <c r="D20" s="175"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
       <c r="E20" s="71">
         <v>0</v>
       </c>
-      <c r="F20" s="176" t="s">
+      <c r="F20" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="102">
+      <c r="G20" s="76">
         <v>60000</v>
       </c>
-      <c r="H20" s="82"/>
-      <c r="I20" s="94">
+      <c r="H20" s="77"/>
+      <c r="I20" s="80">
         <f t="shared" ref="I20:I21" si="0">G20*E20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="82"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="93"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="79"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="141"/>
       <c r="B21" s="47" t="s">
         <v>55</v>
       </c>
@@ -2650,47 +2650,47 @@
       <c r="F21" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="76">
+      <c r="G21" s="142">
         <v>60000</v>
       </c>
-      <c r="H21" s="75"/>
-      <c r="I21" s="74">
+      <c r="H21" s="143"/>
+      <c r="I21" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="75"/>
-      <c r="K21" s="72" t="s">
+      <c r="J21" s="143"/>
+      <c r="K21" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="73"/>
+      <c r="L21" s="174"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="121" t="s">
+      <c r="B22" s="139"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="122"/>
+      <c r="F22" s="137"/>
       <c r="G22" s="52">
         <v>0</v>
       </c>
       <c r="H22" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="100">
+      <c r="I22" s="83">
         <f>SUM(I23:J24)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="101"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="99"/>
+      <c r="J22" s="152"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="165"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="140" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="32" t="s">
@@ -2704,20 +2704,20 @@
       <c r="F23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="102">
+      <c r="G23" s="76">
         <v>60000</v>
       </c>
-      <c r="H23" s="82"/>
-      <c r="I23" s="94">
+      <c r="H23" s="77"/>
+      <c r="I23" s="80">
         <f>G23*E23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="82"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="93"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="79"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A24" s="88"/>
+      <c r="A24" s="141"/>
       <c r="B24" s="47" t="s">
         <v>32</v>
       </c>
@@ -2730,43 +2730,43 @@
       <c r="F24" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="76">
+      <c r="G24" s="142">
         <v>50000</v>
       </c>
-      <c r="H24" s="75"/>
-      <c r="I24" s="74">
+      <c r="H24" s="143"/>
+      <c r="I24" s="164">
         <f>G24*E24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="75"/>
-      <c r="K24" s="164"/>
-      <c r="L24" s="165"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="166"/>
+      <c r="L24" s="167"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="122"/>
+      <c r="B25" s="139"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="137"/>
       <c r="G25" s="56">
         <v>0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="100">
+      <c r="I25" s="83">
         <f>SUM(I26:J27)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="171"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="170"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="82"/>
     </row>
     <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="140" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="32" t="s">
@@ -2780,20 +2780,20 @@
       <c r="F26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="102">
+      <c r="G26" s="76">
         <v>50000</v>
       </c>
-      <c r="H26" s="82"/>
-      <c r="I26" s="94">
+      <c r="H26" s="77"/>
+      <c r="I26" s="80">
         <f t="shared" ref="I26" si="1">G26*E26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="82"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="93"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="79"/>
     </row>
     <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A27" s="87"/>
+      <c r="A27" s="171"/>
       <c r="B27" s="32" t="s">
         <v>35</v>
       </c>
@@ -2806,19 +2806,19 @@
       <c r="F27" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="102">
+      <c r="G27" s="76">
         <v>4500</v>
       </c>
-      <c r="H27" s="82"/>
-      <c r="I27" s="94">
+      <c r="H27" s="77"/>
+      <c r="I27" s="80">
         <f>G27*E27</f>
         <v>0</v>
       </c>
-      <c r="J27" s="82"/>
-      <c r="K27" s="168" t="s">
+      <c r="J27" s="77"/>
+      <c r="K27" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="169"/>
+      <c r="L27" s="90"/>
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1">
       <c r="A28" s="64"/>
@@ -2989,94 +2989,94 @@
       <c r="L39" s="58"/>
     </row>
     <row r="40" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="169" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="166"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="82"/>
-      <c r="I40" s="167">
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="87">
         <f>SUM(I14,I22,I19,I25)</f>
         <v>1440000</v>
       </c>
-      <c r="J40" s="82"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="93"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="88"/>
+      <c r="L40" s="79"/>
     </row>
     <row r="41" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A41" s="83" t="s">
+      <c r="A41" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="85"/>
+      <c r="B41" s="159"/>
+      <c r="C41" s="159"/>
+      <c r="D41" s="100"/>
       <c r="E41" s="39"/>
       <c r="F41" s="40"/>
       <c r="G41" s="41"/>
       <c r="H41" s="42"/>
-      <c r="I41" s="156">
+      <c r="I41" s="99">
         <f>I40</f>
         <v>1440000</v>
       </c>
-      <c r="J41" s="85"/>
-      <c r="K41" s="157"/>
-      <c r="L41" s="158"/>
+      <c r="J41" s="100"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="102"/>
     </row>
     <row r="42" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A42" s="162" t="s">
+      <c r="A42" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="82"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="77"/>
       <c r="E42" s="43"/>
       <c r="F42" s="43"/>
-      <c r="G42" s="159"/>
-      <c r="H42" s="82"/>
-      <c r="I42" s="160">
+      <c r="G42" s="103"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="104">
         <f>I41*0.1</f>
         <v>144000</v>
       </c>
-      <c r="J42" s="82"/>
-      <c r="K42" s="161"/>
-      <c r="L42" s="93"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="88"/>
+      <c r="L42" s="79"/>
     </row>
     <row r="43" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A43" s="163" t="s">
+      <c r="A43" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="152"/>
+      <c r="B43" s="107"/>
+      <c r="C43" s="107"/>
+      <c r="D43" s="92"/>
       <c r="E43" s="44"/>
       <c r="F43" s="44"/>
-      <c r="G43" s="151"/>
-      <c r="H43" s="152"/>
-      <c r="I43" s="153">
+      <c r="G43" s="91"/>
+      <c r="H43" s="92"/>
+      <c r="I43" s="93">
         <f>ROUND(SUM(I41:J42),0)</f>
         <v>1584000</v>
       </c>
-      <c r="J43" s="152"/>
-      <c r="K43" s="154"/>
-      <c r="L43" s="97"/>
+      <c r="J43" s="92"/>
+      <c r="K43" s="94"/>
+      <c r="L43" s="95"/>
     </row>
     <row r="44" spans="1:12" ht="13.5">
-      <c r="A44" s="155"/>
-      <c r="B44" s="135"/>
-      <c r="C44" s="135"/>
-      <c r="D44" s="135"/>
-      <c r="E44" s="135"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="135"/>
-      <c r="H44" s="135"/>
-      <c r="I44" s="135"/>
-      <c r="J44" s="135"/>
-      <c r="K44" s="135"/>
-      <c r="L44" s="136"/>
+      <c r="A44" s="96"/>
+      <c r="B44" s="97"/>
+      <c r="C44" s="97"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="97"/>
+      <c r="F44" s="97"/>
+      <c r="G44" s="97"/>
+      <c r="H44" s="97"/>
+      <c r="I44" s="97"/>
+      <c r="J44" s="97"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="98"/>
     </row>
     <row r="45" spans="1:12" ht="13.5">
       <c r="A45" s="46"/>
@@ -16380,28 +16380,61 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="H6:L6"/>
     <mergeCell ref="B8:D8"/>
@@ -16414,64 +16447,31 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G16:H16"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I25:J25"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/sample/디지털.xlsx
+++ b/sample/디지털.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409C9C21-4C48-4738-9DF4-80E4A50D9A4E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC107F8-F505-4EFE-8966-5808CDA27AF2}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24480" yWindow="1092" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="1365" windowWidth="27000" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="2" r:id="rId1"/>
@@ -1358,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1546,9 +1546,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1561,74 +1558,122 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1638,9 +1683,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1648,6 +1690,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1677,48 +1721,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1727,51 +1730,58 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2179,14 +2189,14 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="118" t="s">
+      <c r="D1" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="138"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2195,12 +2205,12 @@
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="98"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="140"/>
       <c r="J2" s="6"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2223,119 +2233,119 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="121">
+      <c r="B4" s="141">
         <v>46225</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="123"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="143"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="124" t="s">
+      <c r="F4" s="144" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="128" t="s">
+      <c r="H4" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="129"/>
+      <c r="I4" s="149"/>
       <c r="J4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="130" t="s">
+      <c r="K4" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="131"/>
+      <c r="L4" s="151"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="114"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="125"/>
+      <c r="F5" s="145"/>
       <c r="G5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="109"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="128"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1">
-      <c r="A6" s="154" t="s">
+      <c r="A6" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="113"/>
-      <c r="C6" s="113"/>
-      <c r="D6" s="114"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="133"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="126"/>
+      <c r="F6" s="146"/>
       <c r="G6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="78" t="s">
+      <c r="H6" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="111"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="130"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="153" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="155" t="str">
+      <c r="B7" s="158" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
         <v>일백오십팔만사천원정</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="157"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="160"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="125"/>
+      <c r="F7" s="145"/>
       <c r="G7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="135" t="s">
+      <c r="H7" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="151"/>
+      <c r="I7" s="156"/>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="135" t="s">
+      <c r="K7" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="109"/>
+      <c r="L7" s="128"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="134"/>
-      <c r="B8" s="112">
+      <c r="A8" s="154"/>
+      <c r="B8" s="131">
         <f>I11</f>
         <v>1584000</v>
       </c>
-      <c r="C8" s="113"/>
-      <c r="D8" s="114"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="133"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="127"/>
+      <c r="F8" s="147"/>
       <c r="G8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="115" t="s">
+      <c r="H8" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="116"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="117"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="134"/>
+      <c r="K8" s="134"/>
+      <c r="L8" s="135"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="A9" s="19"/>
@@ -2355,18 +2365,18 @@
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="158" t="s">
+      <c r="B10" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="160" t="s">
+      <c r="F10" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="161"/>
+      <c r="G10" s="106"/>
       <c r="H10" s="25" t="s">
         <v>21</v>
       </c>
@@ -2387,29 +2397,29 @@
       <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="115" t="str">
+      <c r="B11" s="107" t="str">
         <f>A5</f>
         <v xml:space="preserve"> 한국교육학술정보원</v>
       </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
       <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="162" t="s">
+      <c r="F11" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="163"/>
+      <c r="G11" s="110"/>
       <c r="H11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="168">
+      <c r="I11" s="111">
         <f>I43</f>
         <v>1584000</v>
       </c>
-      <c r="J11" s="107"/>
-      <c r="K11" s="107"/>
-      <c r="L11" s="95"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="112"/>
     </row>
     <row r="12" spans="1:12" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="21"/>
@@ -2426,56 +2436,56 @@
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="144" t="s">
+      <c r="A13" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="145"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="146"/>
-      <c r="E13" s="153" t="s">
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="146"/>
-      <c r="G13" s="175" t="s">
+      <c r="F13" s="115"/>
+      <c r="G13" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="146"/>
-      <c r="I13" s="153" t="s">
+      <c r="H13" s="115"/>
+      <c r="I13" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="146"/>
-      <c r="K13" s="175" t="s">
+      <c r="J13" s="115"/>
+      <c r="K13" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="176"/>
+      <c r="L13" s="117"/>
     </row>
     <row r="14" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A14" s="138" t="s">
+      <c r="A14" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="139"/>
-      <c r="C14" s="139"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="136" t="s">
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="137"/>
+      <c r="F14" s="124"/>
       <c r="G14" s="53">
         <v>90</v>
       </c>
       <c r="H14" s="54">
         <v>40</v>
       </c>
-      <c r="I14" s="83">
+      <c r="I14" s="98">
         <f>SUM(I15:J18)</f>
         <v>1440000</v>
       </c>
-      <c r="J14" s="152"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="165"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="97"/>
     </row>
     <row r="15" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="125" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="32" t="s">
@@ -2489,20 +2499,20 @@
       <c r="F15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="118">
         <v>300000</v>
       </c>
-      <c r="H15" s="77"/>
-      <c r="I15" s="80">
+      <c r="H15" s="81"/>
+      <c r="I15" s="95">
         <f>G15*E15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="77"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="79"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="92"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A16" s="150"/>
+      <c r="A16" s="126"/>
       <c r="B16" s="32" t="s">
         <v>16</v>
       </c>
@@ -2514,20 +2524,20 @@
       <c r="F16" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="76">
+      <c r="G16" s="118">
         <v>10040</v>
       </c>
-      <c r="H16" s="77"/>
-      <c r="I16" s="80">
+      <c r="H16" s="81"/>
+      <c r="I16" s="95">
         <f>G16*E16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="77"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="91"/>
+      <c r="L16" s="92"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="147" t="s">
+      <c r="A17" s="121" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="32" t="s">
@@ -2543,20 +2553,20 @@
       <c r="F17" s="38">
         <v>90</v>
       </c>
-      <c r="G17" s="76">
+      <c r="G17" s="118">
         <v>300</v>
       </c>
-      <c r="H17" s="77"/>
-      <c r="I17" s="80">
+      <c r="H17" s="81"/>
+      <c r="I17" s="95">
         <f>E17*F17*G17</f>
         <v>1080000</v>
       </c>
-      <c r="J17" s="77"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="79"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="92"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="148"/>
+      <c r="A18" s="122"/>
       <c r="B18" s="34" t="s">
         <v>59</v>
       </c>
@@ -2570,74 +2580,74 @@
       <c r="F18" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="118">
         <v>4000</v>
       </c>
-      <c r="H18" s="77"/>
-      <c r="I18" s="80">
+      <c r="H18" s="81"/>
+      <c r="I18" s="95">
         <f>G18*E18</f>
         <v>360000</v>
       </c>
-      <c r="J18" s="77"/>
-      <c r="K18" s="78" t="s">
+      <c r="J18" s="81"/>
+      <c r="K18" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="79"/>
+      <c r="L18" s="92"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A19" s="138" t="s">
+      <c r="A19" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="136" t="s">
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="137"/>
+      <c r="F19" s="124"/>
       <c r="G19" s="52">
         <v>0</v>
       </c>
       <c r="H19" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="83">
+      <c r="I19" s="98">
         <f>SUM(I20:J21)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="152"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="165"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="97"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A20" s="172" t="s">
+      <c r="A20" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="71">
+      <c r="C20" s="72"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="77">
         <v>0</v>
       </c>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="118">
         <v>60000</v>
       </c>
-      <c r="H20" s="77"/>
-      <c r="I20" s="80">
+      <c r="H20" s="81"/>
+      <c r="I20" s="95">
         <f t="shared" ref="I20:I21" si="0">G20*E20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="77"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="79"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="92"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="141"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="47" t="s">
         <v>55</v>
       </c>
@@ -2650,47 +2660,47 @@
       <c r="F21" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="142">
+      <c r="G21" s="113">
         <v>60000</v>
       </c>
-      <c r="H21" s="143"/>
-      <c r="I21" s="164">
+      <c r="H21" s="94"/>
+      <c r="I21" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="143"/>
-      <c r="K21" s="173" t="s">
+      <c r="J21" s="94"/>
+      <c r="K21" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="174"/>
+      <c r="L21" s="103"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A22" s="138" t="s">
+      <c r="A22" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="139"/>
-      <c r="C22" s="139"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="136" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="137"/>
+      <c r="F22" s="124"/>
       <c r="G22" s="52">
         <v>0</v>
       </c>
       <c r="H22" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="83">
+      <c r="I22" s="98">
         <f>SUM(I23:J24)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="152"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="165"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="97"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A23" s="140" t="s">
+      <c r="A23" s="85" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="32" t="s">
@@ -2704,20 +2714,20 @@
       <c r="F23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="118">
         <v>60000</v>
       </c>
-      <c r="H23" s="77"/>
-      <c r="I23" s="80">
+      <c r="H23" s="81"/>
+      <c r="I23" s="95">
         <f>G23*E23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="77"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="79"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="92"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A24" s="141"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="47" t="s">
         <v>32</v>
       </c>
@@ -2730,70 +2740,70 @@
       <c r="F24" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="142">
+      <c r="G24" s="113">
         <v>50000</v>
       </c>
-      <c r="H24" s="143"/>
-      <c r="I24" s="164">
+      <c r="H24" s="94"/>
+      <c r="I24" s="93">
         <f>G24*E24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="143"/>
-      <c r="K24" s="166"/>
-      <c r="L24" s="167"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="101"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A25" s="138" t="s">
+      <c r="A25" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="139"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="137"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="124"/>
       <c r="G25" s="56">
         <v>0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="83">
+      <c r="I25" s="98">
         <f>SUM(I26:J27)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="84"/>
-      <c r="K25" s="81"/>
-      <c r="L25" s="82"/>
+      <c r="J25" s="179"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="178"/>
     </row>
     <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A26" s="140" t="s">
+      <c r="A26" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="60">
+      <c r="C26" s="72"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="77">
         <v>0</v>
       </c>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="76">
+      <c r="G26" s="118">
         <v>50000</v>
       </c>
-      <c r="H26" s="77"/>
-      <c r="I26" s="80">
+      <c r="H26" s="81"/>
+      <c r="I26" s="95">
         <f t="shared" ref="I26" si="1">G26*E26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="77"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="79"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="92"/>
     </row>
     <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A27" s="171"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="32" t="s">
         <v>35</v>
       </c>
@@ -2806,33 +2816,33 @@
       <c r="F27" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="76">
+      <c r="G27" s="118">
         <v>4500</v>
       </c>
-      <c r="H27" s="77"/>
-      <c r="I27" s="80">
+      <c r="H27" s="81"/>
+      <c r="I27" s="95">
         <f>G27*E27</f>
         <v>0</v>
       </c>
-      <c r="J27" s="77"/>
-      <c r="K27" s="89" t="s">
+      <c r="J27" s="81"/>
+      <c r="K27" s="176" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="90"/>
+      <c r="L27" s="177"/>
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A28" s="64"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="59"/>
+      <c r="A28" s="180"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="75"/>
       <c r="K28" s="61"/>
-      <c r="L28" s="58"/>
+      <c r="L28" s="76"/>
     </row>
     <row r="29" spans="1:12" ht="24.95" customHeight="1">
       <c r="A29" s="64"/>
@@ -2989,94 +2999,94 @@
       <c r="L39" s="58"/>
     </row>
     <row r="40" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A40" s="169" t="s">
+      <c r="A40" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="86"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="87">
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="174"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="175">
         <f>SUM(I14,I22,I19,I25)</f>
         <v>1440000</v>
       </c>
-      <c r="J40" s="77"/>
-      <c r="K40" s="88"/>
-      <c r="L40" s="79"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="171"/>
+      <c r="L40" s="92"/>
     </row>
     <row r="41" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A41" s="170" t="s">
+      <c r="A41" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="159"/>
-      <c r="C41" s="159"/>
-      <c r="D41" s="100"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="84"/>
       <c r="E41" s="39"/>
       <c r="F41" s="40"/>
       <c r="G41" s="41"/>
       <c r="H41" s="42"/>
-      <c r="I41" s="99">
+      <c r="I41" s="166">
         <f>I40</f>
         <v>1440000</v>
       </c>
-      <c r="J41" s="100"/>
-      <c r="K41" s="101"/>
-      <c r="L41" s="102"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="167"/>
+      <c r="L41" s="168"/>
     </row>
     <row r="42" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A42" s="105" t="s">
+      <c r="A42" s="172" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="77"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="81"/>
       <c r="E42" s="43"/>
       <c r="F42" s="43"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="104">
+      <c r="G42" s="169"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="170">
         <f>I41*0.1</f>
         <v>144000</v>
       </c>
-      <c r="J42" s="77"/>
-      <c r="K42" s="88"/>
-      <c r="L42" s="79"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="171"/>
+      <c r="L42" s="92"/>
     </row>
     <row r="43" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A43" s="106" t="s">
+      <c r="A43" s="173" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="92"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="162"/>
       <c r="E43" s="44"/>
       <c r="F43" s="44"/>
-      <c r="G43" s="91"/>
-      <c r="H43" s="92"/>
-      <c r="I43" s="93">
+      <c r="G43" s="161"/>
+      <c r="H43" s="162"/>
+      <c r="I43" s="163">
         <f>ROUND(SUM(I41:J42),0)</f>
         <v>1584000</v>
       </c>
-      <c r="J43" s="92"/>
-      <c r="K43" s="94"/>
-      <c r="L43" s="95"/>
+      <c r="J43" s="162"/>
+      <c r="K43" s="164"/>
+      <c r="L43" s="112"/>
     </row>
     <row r="44" spans="1:12" ht="13.5">
-      <c r="A44" s="96"/>
-      <c r="B44" s="97"/>
-      <c r="C44" s="97"/>
-      <c r="D44" s="97"/>
-      <c r="E44" s="97"/>
-      <c r="F44" s="97"/>
-      <c r="G44" s="97"/>
-      <c r="H44" s="97"/>
-      <c r="I44" s="97"/>
-      <c r="J44" s="97"/>
-      <c r="K44" s="97"/>
-      <c r="L44" s="98"/>
+      <c r="A44" s="165"/>
+      <c r="B44" s="139"/>
+      <c r="C44" s="139"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="139"/>
+      <c r="H44" s="139"/>
+      <c r="I44" s="139"/>
+      <c r="J44" s="139"/>
+      <c r="K44" s="139"/>
+      <c r="L44" s="140"/>
     </row>
     <row r="45" spans="1:12" ht="13.5">
       <c r="A45" s="46"/>
@@ -16380,12 +16390,76 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="D1:I2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I15:J15"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="K15:L15"/>
@@ -16402,76 +16476,12 @@
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="D1:I2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A25:D25"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/sample/디지털.xlsx
+++ b/sample/디지털.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC107F8-F505-4EFE-8966-5808CDA27AF2}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F57200-04C2-4401-B774-4CF9D854D1A4}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="1365" windowWidth="27000" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="27000" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$L$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$L$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
   <si>
     <t xml:space="preserve">  견   적   서</t>
   </si>
@@ -153,10 +153,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>A4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>표지 디자인</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -245,19 +241,34 @@
     <t>무선제본</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>내지</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑백</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>디지털인쇄</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="176" formatCode="yyyy\.\ m\.\ d"/>
     <numFmt numFmtId="177" formatCode="[$₩-412]#,##0"/>
     <numFmt numFmtId="178" formatCode="#,##0\ &quot;컷&quot;\ &quot;기&quot;&quot;준&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0\ \P"/>
     <numFmt numFmtId="180" formatCode="#,##0&quot;부&quot;"/>
     <numFmt numFmtId="181" formatCode="#,##0\ &quot;부&quot;"/>
-    <numFmt numFmtId="182" formatCode="#,##0&quot;P&quot;"/>
     <numFmt numFmtId="183" formatCode="#,##0\P"/>
   </numFmts>
   <fonts count="22">
@@ -434,7 +445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="75">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -990,69 +1001,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top style="double">
         <color rgb="FF000000"/>
       </top>
@@ -1354,11 +1302,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1450,7 +1494,7 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1459,31 +1503,31 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="183" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1494,28 +1538,22 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1533,7 +1571,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1546,16 +1584,16 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1564,116 +1602,81 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1683,6 +1686,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1690,8 +1696,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1730,57 +1734,112 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2170,16 +2229,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L994"/>
+  <dimension ref="A1:L995"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="7.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="7.5703125" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
     <col min="9" max="9" width="8.140625" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
     <col min="11" max="12" width="10.140625" customWidth="1"/>
@@ -2189,14 +2248,14 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="136" t="s">
+      <c r="D1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="138"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="124"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2205,12 +2264,12 @@
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="140"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="6"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2233,119 +2292,119 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="141">
+      <c r="B4" s="125">
         <v>46225</v>
       </c>
-      <c r="C4" s="142"/>
-      <c r="D4" s="143"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="127"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="144" t="s">
-        <v>58</v>
+      <c r="F4" s="128" t="s">
+        <v>57</v>
       </c>
-      <c r="G4" s="57" t="s">
-        <v>51</v>
+      <c r="G4" s="55" t="s">
+        <v>50</v>
       </c>
-      <c r="H4" s="148" t="s">
+      <c r="H4" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="149"/>
+      <c r="I4" s="133"/>
       <c r="J4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="150" t="s">
+      <c r="K4" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="151"/>
+      <c r="L4" s="135"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="132"/>
-      <c r="C5" s="133"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
       <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="145"/>
+      <c r="F5" s="129"/>
       <c r="G5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="91" t="s">
-        <v>62</v>
+      <c r="H5" s="82" t="s">
+        <v>61</v>
       </c>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="128"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="113"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="133"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="118"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="146"/>
+      <c r="F6" s="130"/>
       <c r="G6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="91" t="s">
-        <v>61</v>
+      <c r="H6" s="82" t="s">
+        <v>60</v>
       </c>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="130"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="115"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="158" t="str">
+      <c r="B7" s="142" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
-        <v>일백오십팔만사천원정</v>
+        <v>일백구십만팔백원정</v>
       </c>
-      <c r="C7" s="159"/>
-      <c r="D7" s="160"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="144"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="145"/>
+      <c r="F7" s="129"/>
       <c r="G7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="155" t="s">
+      <c r="H7" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="156"/>
+      <c r="I7" s="140"/>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="155" t="s">
+      <c r="K7" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="128"/>
+      <c r="L7" s="113"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="154"/>
-      <c r="B8" s="131">
+      <c r="A8" s="138"/>
+      <c r="B8" s="116">
         <f>I11</f>
-        <v>1584000</v>
+        <v>1900800</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="133"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="118"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="147"/>
+      <c r="F8" s="131"/>
       <c r="G8" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
-      <c r="H8" s="107" t="s">
+      <c r="H8" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="134"/>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
-      <c r="L8" s="135"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="120"/>
+      <c r="L8" s="121"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="A9" s="19"/>
@@ -2365,18 +2424,18 @@
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="105" t="s">
+      <c r="F10" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="106"/>
+      <c r="G10" s="160"/>
       <c r="H10" s="25" t="s">
         <v>21</v>
       </c>
@@ -2390,36 +2449,36 @@
         <v>16</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="42" customHeight="1" thickBot="1">
       <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="107" t="str">
+      <c r="B11" s="119" t="str">
         <f>A5</f>
         <v xml:space="preserve"> 한국교육학술정보원</v>
       </c>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
       <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="109" t="s">
+      <c r="F11" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="110"/>
+      <c r="G11" s="162"/>
       <c r="H11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="111">
-        <f>I43</f>
-        <v>1584000</v>
+      <c r="I11" s="163">
+        <f>I44</f>
+        <v>1900800</v>
       </c>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="112"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="99"/>
     </row>
     <row r="12" spans="1:12" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="21"/>
@@ -2436,60 +2495,62 @@
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="119" t="s">
+      <c r="A13" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="114" t="s">
+      <c r="B13" s="178"/>
+      <c r="C13" s="178"/>
+      <c r="D13" s="179"/>
+      <c r="E13" s="180" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="115"/>
-      <c r="G13" s="116" t="s">
+      <c r="F13" s="179"/>
+      <c r="G13" s="181" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="115"/>
-      <c r="I13" s="114" t="s">
+      <c r="H13" s="179"/>
+      <c r="I13" s="180" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="115"/>
-      <c r="K13" s="116" t="s">
+      <c r="J13" s="179"/>
+      <c r="K13" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="117"/>
+      <c r="L13" s="182"/>
     </row>
     <row r="14" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="123" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="124"/>
-      <c r="G14" s="53">
+      <c r="B14" s="148"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="58">
         <v>90</v>
       </c>
-      <c r="H14" s="54">
-        <v>40</v>
+      <c r="F14" s="36" t="s">
+        <v>33</v>
       </c>
-      <c r="I14" s="98">
-        <f>SUM(I15:J18)</f>
-        <v>1440000</v>
+      <c r="G14" s="184">
+        <v>80</v>
       </c>
-      <c r="J14" s="99"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="97"/>
+      <c r="H14" s="185" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="175">
+        <f>SUM(I15:J19)</f>
+        <v>1728000</v>
+      </c>
+      <c r="J14" s="176"/>
+      <c r="K14" s="186"/>
+      <c r="L14" s="187"/>
     </row>
     <row r="15" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="155" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="33"/>
@@ -2499,20 +2560,20 @@
       <c r="F15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="118">
+      <c r="G15" s="80">
         <v>300000</v>
       </c>
       <c r="H15" s="81"/>
-      <c r="I15" s="95">
+      <c r="I15" s="84">
         <f>G15*E15</f>
         <v>0</v>
       </c>
       <c r="J15" s="81"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="92"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="83"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A16" s="126"/>
+      <c r="A16" s="156"/>
       <c r="B16" s="32" t="s">
         <v>16</v>
       </c>
@@ -2522,22 +2583,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
-      <c r="G16" s="118">
+      <c r="G16" s="80">
         <v>10040</v>
       </c>
       <c r="H16" s="81"/>
-      <c r="I16" s="95">
+      <c r="I16" s="84">
         <f>G16*E16</f>
         <v>0</v>
       </c>
       <c r="J16" s="81"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="92"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="83"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="153" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="32" t="s">
@@ -2545,562 +2606,583 @@
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="37">
         <v>40</v>
       </c>
       <c r="F17" s="38">
+        <f>E14</f>
         <v>90</v>
       </c>
-      <c r="G17" s="118">
+      <c r="G17" s="80">
         <v>300</v>
       </c>
       <c r="H17" s="81"/>
-      <c r="I17" s="95">
+      <c r="I17" s="84">
         <f>E17*F17*G17</f>
         <v>1080000</v>
       </c>
       <c r="J17" s="81"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="92"/>
+      <c r="K17" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="83"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="122"/>
-      <c r="B18" s="34" t="s">
-        <v>59</v>
+      <c r="A18" s="153"/>
+      <c r="B18" s="32" t="s">
+        <v>63</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="37">
+        <f>G14-E17</f>
+        <v>40</v>
+      </c>
+      <c r="F18" s="38">
+        <f>E14</f>
         <v>90</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="G18" s="80">
+        <v>80</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="84">
+        <f>E18*F18*G18</f>
+        <v>288000</v>
+      </c>
+      <c r="J18" s="81"/>
+      <c r="K18" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="L18" s="83"/>
+    </row>
+    <row r="19" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A19" s="154"/>
+      <c r="B19" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="35">
+        <f>E14</f>
+        <v>90</v>
+      </c>
+      <c r="F19" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="118">
+      <c r="G19" s="80">
         <v>4000</v>
       </c>
-      <c r="H18" s="81"/>
-      <c r="I18" s="95">
-        <f>G18*E18</f>
+      <c r="H19" s="81"/>
+      <c r="I19" s="84">
+        <f>G19*E19</f>
         <v>360000</v>
       </c>
-      <c r="J18" s="81"/>
-      <c r="K18" s="91" t="s">
-        <v>60</v>
+      <c r="J19" s="81"/>
+      <c r="K19" s="82" t="s">
+        <v>59</v>
       </c>
-      <c r="L18" s="92"/>
-    </row>
-    <row r="19" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A19" s="89" t="s">
+      <c r="L19" s="83"/>
+    </row>
+    <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
+      <c r="A20" s="147" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="148"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="148"/>
+      <c r="E20" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="123" t="s">
+      <c r="F20" s="146"/>
+      <c r="G20" s="52">
+        <v>0</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="87">
+        <f>SUM(I21:J22)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="165"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="164"/>
+    </row>
+    <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1">
+      <c r="A21" s="173" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="75">
+        <v>0</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="80">
+        <v>60000</v>
+      </c>
+      <c r="H21" s="81"/>
+      <c r="I21" s="84">
+        <f t="shared" ref="I21:I22" si="0">G21*E21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="81"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="83"/>
+    </row>
+    <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
+      <c r="A22" s="150"/>
+      <c r="B22" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="124"/>
-      <c r="G19" s="52">
+      <c r="C22" s="48"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="50">
+        <f>G20</f>
         <v>0</v>
       </c>
-      <c r="H19" s="55" t="s">
-        <v>44</v>
+      <c r="F22" s="51" t="s">
+        <v>33</v>
       </c>
-      <c r="I19" s="98">
-        <f>SUM(I20:J21)</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="99"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="97"/>
-    </row>
-    <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A20" s="87" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="77">
-        <v>0</v>
-      </c>
-      <c r="F20" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="118">
+      <c r="G22" s="151">
         <v>60000</v>
       </c>
-      <c r="H20" s="81"/>
-      <c r="I20" s="95">
-        <f t="shared" ref="I20:I21" si="0">G20*E20</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="81"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="92"/>
-    </row>
-    <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="88"/>
-      <c r="B21" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="50">
-        <f>G19</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="113">
-        <v>60000</v>
-      </c>
-      <c r="H21" s="94"/>
-      <c r="I21" s="93">
+      <c r="H22" s="152"/>
+      <c r="I22" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="94"/>
-      <c r="K21" s="102" t="s">
-        <v>56</v>
+      <c r="J22" s="152"/>
+      <c r="K22" s="169" t="s">
+        <v>55</v>
       </c>
-      <c r="L21" s="103"/>
-    </row>
-    <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A22" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="123" t="s">
+      <c r="L22" s="170"/>
+    </row>
+    <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
+      <c r="A23" s="147" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="124"/>
-      <c r="G22" s="52">
+      <c r="B23" s="148"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="145" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="146"/>
+      <c r="G23" s="52">
         <v>0</v>
       </c>
-      <c r="H22" s="55" t="s">
-        <v>44</v>
+      <c r="H23" s="53" t="s">
+        <v>43</v>
       </c>
-      <c r="I22" s="98">
-        <f>SUM(I23:J24)</f>
+      <c r="I23" s="87">
+        <f>SUM(I24:J25)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="99"/>
-      <c r="K22" s="96"/>
-      <c r="L22" s="97"/>
-    </row>
-    <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A23" s="85" t="s">
+      <c r="J23" s="165"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="164"/>
+    </row>
+    <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1">
+      <c r="A24" s="149" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B24" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="60">
+      <c r="C24" s="34"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="58">
         <v>0</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F24" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="118">
+      <c r="G24" s="80">
         <v>60000</v>
       </c>
-      <c r="H23" s="81"/>
-      <c r="I23" s="95">
-        <f>G23*E23</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="81"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="92"/>
-    </row>
-    <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A24" s="88"/>
-      <c r="B24" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="50">
-        <f>G22</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="113">
-        <v>50000</v>
-      </c>
-      <c r="H24" s="94"/>
-      <c r="I24" s="93">
+      <c r="H24" s="81"/>
+      <c r="I24" s="84">
         <f>G24*E24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="94"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="101"/>
-    </row>
-    <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A25" s="89" t="s">
-        <v>50</v>
+      <c r="J24" s="81"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="83"/>
+    </row>
+    <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
+      <c r="A25" s="150"/>
+      <c r="B25" s="47" t="s">
+        <v>32</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="124"/>
-      <c r="G25" s="56">
+      <c r="C25" s="48"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="50">
+        <f>G23</f>
         <v>0</v>
       </c>
-      <c r="H25" s="55" t="s">
-        <v>44</v>
+      <c r="F25" s="51" t="s">
+        <v>33</v>
       </c>
-      <c r="I25" s="98">
-        <f>SUM(I26:J27)</f>
+      <c r="G25" s="151">
+        <v>50000</v>
+      </c>
+      <c r="H25" s="152"/>
+      <c r="I25" s="166">
+        <f>G25*E25</f>
         <v>0</v>
       </c>
-      <c r="J25" s="179"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="178"/>
-    </row>
-    <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A26" s="87" t="s">
+      <c r="J25" s="152"/>
+      <c r="K25" s="167"/>
+      <c r="L25" s="168"/>
+    </row>
+    <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
+      <c r="A26" s="147" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="148"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="54">
+        <v>0</v>
+      </c>
+      <c r="H26" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="87">
+        <f>SUM(I27:J28)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="88"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="86"/>
+    </row>
+    <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
+      <c r="A27" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="71" t="s">
+      <c r="B27" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="77">
+      <c r="C27" s="70"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="75">
         <v>0</v>
       </c>
-      <c r="F26" s="74" t="s">
+      <c r="F27" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="118">
+      <c r="G27" s="80">
         <v>50000</v>
       </c>
-      <c r="H26" s="81"/>
-      <c r="I26" s="95">
-        <f t="shared" ref="I26" si="1">G26*E26</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="81"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="92"/>
-    </row>
-    <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A27" s="86"/>
-      <c r="B27" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="60">
-        <f>G25</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="118">
-        <v>4500</v>
-      </c>
       <c r="H27" s="81"/>
-      <c r="I27" s="95">
-        <f>G27*E27</f>
+      <c r="I27" s="84">
+        <f t="shared" ref="I27" si="1">G27*E27</f>
         <v>0</v>
       </c>
       <c r="J27" s="81"/>
-      <c r="K27" s="176" t="s">
-        <v>47</v>
+      <c r="K27" s="82"/>
+      <c r="L27" s="83"/>
+    </row>
+    <row r="28" spans="1:12" ht="24.95" hidden="1" customHeight="1">
+      <c r="A28" s="174"/>
+      <c r="B28" s="32" t="s">
+        <v>35</v>
       </c>
-      <c r="L27" s="177"/>
-    </row>
-    <row r="28" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A28" s="180"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="181"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="75"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="76"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="58">
+        <f>G26</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="80">
+        <v>4500</v>
+      </c>
+      <c r="H28" s="81"/>
+      <c r="I28" s="84">
+        <f>G28*E28</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="81"/>
+      <c r="K28" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" s="94"/>
     </row>
     <row r="29" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="59"/>
-      <c r="K29" s="61"/>
-      <c r="L29" s="58"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="74"/>
     </row>
     <row r="30" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="32"/>
       <c r="C30" s="34"/>
       <c r="D30" s="33"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="56"/>
     </row>
     <row r="31" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A31" s="64"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="32"/>
       <c r="C31" s="34"/>
       <c r="D31" s="33"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="56"/>
     </row>
     <row r="32" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A32" s="64"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="32"/>
       <c r="C32" s="34"/>
       <c r="D32" s="33"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="56"/>
     </row>
     <row r="33" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A33" s="64"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="32"/>
       <c r="C33" s="34"/>
       <c r="D33" s="33"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="59"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="56"/>
     </row>
     <row r="34" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="32"/>
       <c r="C34" s="34"/>
       <c r="D34" s="33"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="56"/>
     </row>
     <row r="35" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A35" s="64"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="32"/>
       <c r="C35" s="34"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="56"/>
     </row>
     <row r="36" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="32"/>
       <c r="C36" s="34"/>
       <c r="D36" s="33"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="59"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="56"/>
     </row>
     <row r="37" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A37" s="64"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="32"/>
       <c r="C37" s="34"/>
       <c r="D37" s="33"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="67"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="56"/>
     </row>
     <row r="38" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="62"/>
       <c r="B38" s="32"/>
       <c r="C38" s="34"/>
       <c r="D38" s="33"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="67"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="65"/>
     </row>
     <row r="39" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A39" s="64"/>
+      <c r="A39" s="62"/>
       <c r="B39" s="32"/>
       <c r="C39" s="34"/>
       <c r="D39" s="33"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="58"/>
-    </row>
-    <row r="40" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A40" s="79" t="s">
+      <c r="E39" s="58"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="66"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="65"/>
+    </row>
+    <row r="40" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A40" s="62"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="56"/>
+    </row>
+    <row r="41" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A41" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="174"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="175">
-        <f>SUM(I14,I22,I19,I25)</f>
-        <v>1440000</v>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="91">
+        <f>SUM(I14,I23,I20,I26)</f>
+        <v>1728000</v>
       </c>
-      <c r="J40" s="81"/>
-      <c r="K40" s="171"/>
-      <c r="L40" s="92"/>
-    </row>
-    <row r="41" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A41" s="82" t="s">
+      <c r="J41" s="81"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="83"/>
+    </row>
+    <row r="42" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A42" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="166">
-        <f>I40</f>
-        <v>1440000</v>
+      <c r="B42" s="158"/>
+      <c r="C42" s="158"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="103">
+        <f>I41</f>
+        <v>1728000</v>
       </c>
-      <c r="J41" s="84"/>
-      <c r="K41" s="167"/>
-      <c r="L41" s="168"/>
-    </row>
-    <row r="42" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A42" s="172" t="s">
+      <c r="J42" s="104"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="106"/>
+    </row>
+    <row r="43" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A43" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="169"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="170">
-        <f>I41*0.1</f>
-        <v>144000</v>
+      <c r="B43" s="90"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="107"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="108">
+        <f>I42*0.1</f>
+        <v>172800</v>
       </c>
-      <c r="J42" s="81"/>
-      <c r="K42" s="171"/>
-      <c r="L42" s="92"/>
-    </row>
-    <row r="43" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A43" s="173" t="s">
+      <c r="J43" s="81"/>
+      <c r="K43" s="92"/>
+      <c r="L43" s="83"/>
+    </row>
+    <row r="44" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A44" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="108"/>
-      <c r="C43" s="108"/>
-      <c r="D43" s="162"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="161"/>
-      <c r="H43" s="162"/>
-      <c r="I43" s="163">
-        <f>ROUND(SUM(I41:J42),0)</f>
-        <v>1584000</v>
+      <c r="B44" s="111"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="95"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="97">
+        <f>ROUND(SUM(I42:J43),0)</f>
+        <v>1900800</v>
       </c>
-      <c r="J43" s="162"/>
-      <c r="K43" s="164"/>
-      <c r="L43" s="112"/>
-    </row>
-    <row r="44" spans="1:12" ht="13.5">
-      <c r="A44" s="165"/>
-      <c r="B44" s="139"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="H44" s="139"/>
-      <c r="I44" s="139"/>
-      <c r="J44" s="139"/>
-      <c r="K44" s="139"/>
-      <c r="L44" s="140"/>
+      <c r="J44" s="96"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="99"/>
     </row>
     <row r="45" spans="1:12" ht="13.5">
-      <c r="A45" s="46"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
+      <c r="A45" s="100"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="101"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="101"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="102"/>
     </row>
     <row r="46" spans="1:12" ht="13.5">
       <c r="A46" s="46"/>
@@ -3138,8 +3220,8 @@
       <c r="E48" s="46"/>
       <c r="F48" s="46"/>
       <c r="G48" s="46"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="46"/>
       <c r="J48" s="46"/>
       <c r="K48" s="46"/>
       <c r="L48" s="46"/>
@@ -3152,8 +3234,8 @@
       <c r="E49" s="46"/>
       <c r="F49" s="46"/>
       <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
       <c r="J49" s="46"/>
       <c r="K49" s="46"/>
       <c r="L49" s="46"/>
@@ -3168,7 +3250,7 @@
       <c r="G50" s="46"/>
       <c r="H50" s="46"/>
       <c r="I50" s="46"/>
-      <c r="J50" s="45"/>
+      <c r="J50" s="46"/>
       <c r="K50" s="46"/>
       <c r="L50" s="46"/>
     </row>
@@ -3182,7 +3264,7 @@
       <c r="G51" s="46"/>
       <c r="H51" s="46"/>
       <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
+      <c r="J51" s="45"/>
       <c r="K51" s="46"/>
       <c r="L51" s="46"/>
     </row>
@@ -3196,7 +3278,7 @@
       <c r="G52" s="46"/>
       <c r="H52" s="46"/>
       <c r="I52" s="46"/>
-      <c r="J52" s="45"/>
+      <c r="J52" s="46"/>
       <c r="K52" s="46"/>
       <c r="L52" s="46"/>
     </row>
@@ -3210,7 +3292,7 @@
       <c r="G53" s="46"/>
       <c r="H53" s="46"/>
       <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
+      <c r="J53" s="45"/>
       <c r="K53" s="46"/>
       <c r="L53" s="46"/>
     </row>
@@ -16388,30 +16470,78 @@
       <c r="K994" s="46"/>
       <c r="L994" s="46"/>
     </row>
+    <row r="995" spans="1:12" ht="13.5">
+      <c r="A995" s="46"/>
+      <c r="B995" s="46"/>
+      <c r="C995" s="46"/>
+      <c r="D995" s="46"/>
+      <c r="E995" s="46"/>
+      <c r="F995" s="46"/>
+      <c r="G995" s="46"/>
+      <c r="H995" s="46"/>
+      <c r="I995" s="46"/>
+      <c r="J995" s="46"/>
+      <c r="K995" s="46"/>
+      <c r="L995" s="46"/>
+    </row>
   </sheetData>
-  <mergeCells count="92">
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I26:J26"/>
+  <mergeCells count="93">
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I20:J20"/>
     <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="H6:L6"/>
     <mergeCell ref="B8:D8"/>
@@ -16427,69 +16557,33 @@
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="87" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="I17" formula="1"/>
-  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/sample/디지털.xlsx
+++ b/sample/디지털.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F57200-04C2-4401-B774-4CF9D854D1A4}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71576C7A-AA5A-474E-9A9D-A41636820D23}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27000" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="27000" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="2" r:id="rId1"/>
@@ -269,7 +269,7 @@
     <numFmt numFmtId="179" formatCode="#,##0\ \P"/>
     <numFmt numFmtId="180" formatCode="#,##0&quot;부&quot;"/>
     <numFmt numFmtId="181" formatCode="#,##0\ &quot;부&quot;"/>
-    <numFmt numFmtId="183" formatCode="#,##0\P"/>
+    <numFmt numFmtId="182" formatCode="#,##0\P"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -445,7 +445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="78">
+  <borders count="77">
     <border>
       <left/>
       <right/>
@@ -1252,17 +1252,6 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1402,7 +1391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1506,7 +1495,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="2" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1559,41 +1548,22 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1609,74 +1579,143 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="13" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1686,9 +1725,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1696,6 +1732,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1734,113 +1772,51 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2248,14 +2224,14 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="122" t="s">
+      <c r="D1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="124"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="139"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2264,12 +2240,12 @@
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="102"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="141"/>
       <c r="J2" s="6"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2292,119 +2268,119 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="125">
+      <c r="B4" s="142">
         <v>46225</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="127"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="144"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="145" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="132" t="s">
+      <c r="H4" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="133"/>
+      <c r="I4" s="150"/>
       <c r="J4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="134" t="s">
+      <c r="K4" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="135"/>
+      <c r="L4" s="152"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="134"/>
       <c r="D5" s="15" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="129"/>
+      <c r="F5" s="146"/>
       <c r="G5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="82" t="s">
+      <c r="H5" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="112"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="113"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="129"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1">
-      <c r="A6" s="141" t="s">
+      <c r="A6" s="158" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="118"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="134"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="130"/>
+      <c r="F6" s="147"/>
       <c r="G6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="82" t="s">
+      <c r="H6" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="115"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="131"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="154" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="142" t="str">
+      <c r="B7" s="159" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
         <v>일백구십만팔백원정</v>
       </c>
-      <c r="C7" s="143"/>
-      <c r="D7" s="144"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="161"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="129"/>
+      <c r="F7" s="146"/>
       <c r="G7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="139" t="s">
+      <c r="H7" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="140"/>
+      <c r="I7" s="157"/>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="139" t="s">
+      <c r="K7" s="156" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="113"/>
+      <c r="L7" s="129"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="138"/>
-      <c r="B8" s="116">
+      <c r="A8" s="155"/>
+      <c r="B8" s="132">
         <f>I11</f>
         <v>1900800</v>
       </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="118"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="134"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="131"/>
+      <c r="F8" s="148"/>
       <c r="G8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="119" t="s">
+      <c r="H8" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="120"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="120"/>
-      <c r="L8" s="121"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="136"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="A9" s="19"/>
@@ -2424,18 +2400,18 @@
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="157" t="s">
+      <c r="B10" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
       <c r="E10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="159" t="s">
+      <c r="F10" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="160"/>
+      <c r="G10" s="103"/>
       <c r="H10" s="25" t="s">
         <v>21</v>
       </c>
@@ -2456,29 +2432,29 @@
       <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="119" t="str">
+      <c r="B11" s="104" t="str">
         <f>A5</f>
         <v xml:space="preserve"> 한국교육학술정보원</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
       <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="161" t="s">
+      <c r="F11" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="162"/>
+      <c r="G11" s="107"/>
       <c r="H11" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="163">
+      <c r="I11" s="108">
         <f>I44</f>
         <v>1900800</v>
       </c>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="99"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="109"/>
     </row>
     <row r="12" spans="1:12" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="21"/>
@@ -2495,58 +2471,58 @@
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="177" t="s">
+      <c r="A13" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="178"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="179"/>
-      <c r="E13" s="180" t="s">
+      <c r="B13" s="119"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="179"/>
-      <c r="G13" s="181" t="s">
+      <c r="F13" s="112"/>
+      <c r="G13" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="179"/>
-      <c r="I13" s="180" t="s">
+      <c r="H13" s="112"/>
+      <c r="I13" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="179"/>
-      <c r="K13" s="181" t="s">
+      <c r="J13" s="112"/>
+      <c r="K13" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="182"/>
+      <c r="L13" s="114"/>
     </row>
     <row r="14" spans="1:12" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A14" s="147" t="s">
+      <c r="A14" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="58">
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="56">
         <v>90</v>
       </c>
       <c r="F14" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="184">
+      <c r="G14" s="73">
         <v>80</v>
       </c>
-      <c r="H14" s="185" t="s">
+      <c r="H14" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="175">
+      <c r="I14" s="116">
         <f>SUM(I15:J19)</f>
         <v>1728000</v>
       </c>
-      <c r="J14" s="176"/>
-      <c r="K14" s="186"/>
-      <c r="L14" s="187"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="76"/>
     </row>
     <row r="15" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="125" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="32" t="s">
@@ -2560,20 +2536,20 @@
       <c r="F15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="80">
+      <c r="G15" s="115">
         <v>300000</v>
       </c>
       <c r="H15" s="81"/>
-      <c r="I15" s="84">
+      <c r="I15" s="92">
         <f>G15*E15</f>
         <v>0</v>
       </c>
       <c r="J15" s="81"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="83"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A16" s="156"/>
+      <c r="A16" s="126"/>
       <c r="B16" s="32" t="s">
         <v>16</v>
       </c>
@@ -2585,20 +2561,20 @@
       <c r="F16" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="80">
+      <c r="G16" s="115">
         <v>10040</v>
       </c>
       <c r="H16" s="81"/>
-      <c r="I16" s="84">
+      <c r="I16" s="92">
         <f>G16*E16</f>
         <v>0</v>
       </c>
       <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A17" s="153" t="s">
+      <c r="A17" s="120" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="32" t="s">
@@ -2615,22 +2591,22 @@
         <f>E14</f>
         <v>90</v>
       </c>
-      <c r="G17" s="80">
+      <c r="G17" s="115">
         <v>300</v>
       </c>
       <c r="H17" s="81"/>
-      <c r="I17" s="84">
+      <c r="I17" s="92">
         <f>E17*F17*G17</f>
         <v>1080000</v>
       </c>
       <c r="J17" s="81"/>
-      <c r="K17" s="82" t="s">
+      <c r="K17" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="L17" s="83"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A18" s="153"/>
+      <c r="A18" s="120"/>
       <c r="B18" s="32" t="s">
         <v>63</v>
       </c>
@@ -2646,22 +2622,22 @@
         <f>E14</f>
         <v>90</v>
       </c>
-      <c r="G18" s="80">
+      <c r="G18" s="115">
         <v>80</v>
       </c>
       <c r="H18" s="81"/>
-      <c r="I18" s="84">
+      <c r="I18" s="92">
         <f>E18*F18*G18</f>
         <v>288000</v>
       </c>
       <c r="J18" s="81"/>
-      <c r="K18" s="82" t="s">
+      <c r="K18" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="L18" s="83"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A19" s="154"/>
+      <c r="A19" s="121"/>
       <c r="B19" s="34" t="s">
         <v>58</v>
       </c>
@@ -2676,74 +2652,74 @@
       <c r="F19" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="80">
+      <c r="G19" s="115">
         <v>4000</v>
       </c>
       <c r="H19" s="81"/>
-      <c r="I19" s="84">
+      <c r="I19" s="92">
         <f>G19*E19</f>
         <v>360000</v>
       </c>
       <c r="J19" s="81"/>
-      <c r="K19" s="82" t="s">
+      <c r="K19" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L19" s="83"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A20" s="147" t="s">
+      <c r="A20" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="148"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="148"/>
-      <c r="E20" s="145" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="146"/>
+      <c r="F20" s="123"/>
       <c r="G20" s="52">
         <v>0</v>
       </c>
       <c r="H20" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="I20" s="87">
+      <c r="I20" s="95">
         <f>SUM(I21:J22)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="165"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="164"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="94"/>
     </row>
     <row r="21" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A21" s="173" t="s">
+      <c r="A21" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="75">
+      <c r="C21" s="59"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="64">
         <v>0</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="80">
+      <c r="G21" s="115">
         <v>60000</v>
       </c>
       <c r="H21" s="81"/>
-      <c r="I21" s="84">
+      <c r="I21" s="92">
         <f t="shared" ref="I21:I22" si="0">G21*E21</f>
         <v>0</v>
       </c>
       <c r="J21" s="81"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="83"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A22" s="150"/>
+      <c r="A22" s="87"/>
       <c r="B22" s="47" t="s">
         <v>54</v>
       </c>
@@ -2756,47 +2732,47 @@
       <c r="F22" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="151">
+      <c r="G22" s="110">
         <v>60000</v>
       </c>
-      <c r="H22" s="152"/>
-      <c r="I22" s="166">
+      <c r="H22" s="91"/>
+      <c r="I22" s="90">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="152"/>
-      <c r="K22" s="169" t="s">
+      <c r="J22" s="91"/>
+      <c r="K22" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="170"/>
+      <c r="L22" s="100"/>
     </row>
     <row r="23" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A23" s="147" t="s">
+      <c r="A23" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="148"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="148"/>
-      <c r="E23" s="145" t="s">
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="146"/>
+      <c r="F23" s="123"/>
       <c r="G23" s="52">
         <v>0</v>
       </c>
       <c r="H23" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="I23" s="87">
+      <c r="I23" s="95">
         <f>SUM(I24:J25)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="165"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="164"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="94"/>
     </row>
     <row r="24" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A24" s="149" t="s">
+      <c r="A24" s="127" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="32" t="s">
@@ -2804,26 +2780,26 @@
       </c>
       <c r="C24" s="34"/>
       <c r="D24" s="33"/>
-      <c r="E24" s="58">
+      <c r="E24" s="56">
         <v>0</v>
       </c>
       <c r="F24" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="80">
+      <c r="G24" s="115">
         <v>60000</v>
       </c>
       <c r="H24" s="81"/>
-      <c r="I24" s="84">
+      <c r="I24" s="92">
         <f>G24*E24</f>
         <v>0</v>
       </c>
       <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="83"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickBot="1">
-      <c r="A25" s="150"/>
+      <c r="A25" s="87"/>
       <c r="B25" s="47" t="s">
         <v>32</v>
       </c>
@@ -2836,353 +2812,353 @@
       <c r="F25" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="151">
+      <c r="G25" s="110">
         <v>50000</v>
       </c>
-      <c r="H25" s="152"/>
-      <c r="I25" s="166">
+      <c r="H25" s="91"/>
+      <c r="I25" s="90">
         <f>G25*E25</f>
         <v>0</v>
       </c>
-      <c r="J25" s="152"/>
-      <c r="K25" s="167"/>
-      <c r="L25" s="168"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="98"/>
     </row>
     <row r="26" spans="1:12" ht="24.95" hidden="1" customHeight="1" thickTop="1">
-      <c r="A26" s="147" t="s">
+      <c r="A26" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="146"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="123"/>
       <c r="G26" s="54">
         <v>0</v>
       </c>
       <c r="H26" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="87">
+      <c r="I26" s="95">
         <f>SUM(I27:J28)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="88"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="86"/>
+      <c r="J26" s="180"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="179"/>
     </row>
     <row r="27" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A27" s="173" t="s">
+      <c r="A27" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="75">
+      <c r="C27" s="59"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="64">
         <v>0</v>
       </c>
-      <c r="F27" s="72" t="s">
+      <c r="F27" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="80">
+      <c r="G27" s="115">
         <v>50000</v>
       </c>
       <c r="H27" s="81"/>
-      <c r="I27" s="84">
+      <c r="I27" s="92">
         <f t="shared" ref="I27" si="1">G27*E27</f>
         <v>0</v>
       </c>
       <c r="J27" s="81"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="83"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="24.95" hidden="1" customHeight="1">
-      <c r="A28" s="174"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="34"/>
       <c r="D28" s="33"/>
-      <c r="E28" s="58">
+      <c r="E28" s="56">
         <f>G26</f>
         <v>0</v>
       </c>
       <c r="F28" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="80">
+      <c r="G28" s="115">
         <v>4500</v>
       </c>
       <c r="H28" s="81"/>
-      <c r="I28" s="84">
+      <c r="I28" s="92">
         <f>G28*E28</f>
         <v>0</v>
       </c>
       <c r="J28" s="81"/>
-      <c r="K28" s="93" t="s">
+      <c r="K28" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="94"/>
+      <c r="L28" s="178"/>
     </row>
     <row r="29" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A29" s="77"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="59"/>
-      <c r="L29" s="74"/>
+      <c r="A29" s="66"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="63"/>
     </row>
     <row r="30" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A30" s="62"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="56"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="70"/>
     </row>
     <row r="31" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A31" s="62"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="56"/>
+      <c r="A31" s="66"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="70"/>
     </row>
     <row r="32" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A32" s="62"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="56"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="70"/>
     </row>
     <row r="33" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A33" s="62"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="59"/>
-      <c r="L33" s="56"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="70"/>
     </row>
     <row r="34" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="56"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="70"/>
     </row>
     <row r="35" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A35" s="62"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="56"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="70"/>
     </row>
     <row r="36" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A36" s="62"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="60"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="56"/>
+      <c r="A36" s="66"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="70"/>
     </row>
     <row r="37" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A37" s="62"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="56"/>
+      <c r="A37" s="66"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="70"/>
     </row>
     <row r="38" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A38" s="62"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="65"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="72"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="70"/>
     </row>
     <row r="39" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A39" s="62"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="66"/>
-      <c r="K39" s="59"/>
-      <c r="L39" s="65"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="70"/>
     </row>
     <row r="40" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A40" s="62"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="60"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="56"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="70"/>
     </row>
     <row r="41" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A41" s="171" t="s">
+      <c r="A41" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
       <c r="D41" s="81"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
+      <c r="E41" s="175"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
       <c r="H41" s="81"/>
-      <c r="I41" s="91">
+      <c r="I41" s="176">
         <f>SUM(I14,I23,I20,I26)</f>
         <v>1728000</v>
       </c>
       <c r="J41" s="81"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="83"/>
+      <c r="K41" s="172"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A42" s="172" t="s">
+      <c r="A42" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="158"/>
-      <c r="C42" s="158"/>
-      <c r="D42" s="104"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="39"/>
       <c r="F42" s="40"/>
       <c r="G42" s="41"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="103">
+      <c r="I42" s="167">
         <f>I41</f>
         <v>1728000</v>
       </c>
-      <c r="J42" s="104"/>
-      <c r="K42" s="105"/>
-      <c r="L42" s="106"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="168"/>
+      <c r="L42" s="169"/>
     </row>
     <row r="43" spans="1:12" ht="24.95" customHeight="1">
-      <c r="A43" s="109" t="s">
+      <c r="A43" s="173" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="90"/>
-      <c r="C43" s="90"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="80"/>
       <c r="D43" s="81"/>
       <c r="E43" s="43"/>
       <c r="F43" s="43"/>
-      <c r="G43" s="107"/>
+      <c r="G43" s="170"/>
       <c r="H43" s="81"/>
-      <c r="I43" s="108">
+      <c r="I43" s="171">
         <f>I42*0.1</f>
         <v>172800</v>
       </c>
       <c r="J43" s="81"/>
-      <c r="K43" s="92"/>
-      <c r="L43" s="83"/>
+      <c r="K43" s="172"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A44" s="110" t="s">
+      <c r="A44" s="174" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="111"/>
-      <c r="C44" s="111"/>
-      <c r="D44" s="96"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="163"/>
       <c r="E44" s="44"/>
       <c r="F44" s="44"/>
-      <c r="G44" s="95"/>
-      <c r="H44" s="96"/>
-      <c r="I44" s="97">
+      <c r="G44" s="162"/>
+      <c r="H44" s="163"/>
+      <c r="I44" s="164">
         <f>ROUND(SUM(I42:J43),0)</f>
         <v>1900800</v>
       </c>
-      <c r="J44" s="96"/>
-      <c r="K44" s="98"/>
-      <c r="L44" s="99"/>
+      <c r="J44" s="163"/>
+      <c r="K44" s="165"/>
+      <c r="L44" s="109"/>
     </row>
     <row r="45" spans="1:12" ht="13.5">
-      <c r="A45" s="100"/>
-      <c r="B45" s="101"/>
-      <c r="C45" s="101"/>
-      <c r="D45" s="101"/>
-      <c r="E45" s="101"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="101"/>
-      <c r="I45" s="101"/>
-      <c r="J45" s="101"/>
-      <c r="K45" s="101"/>
-      <c r="L45" s="102"/>
+      <c r="A45" s="166"/>
+      <c r="B45" s="140"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="140"/>
+      <c r="I45" s="140"/>
+      <c r="J45" s="140"/>
+      <c r="K45" s="140"/>
+      <c r="L45" s="141"/>
     </row>
     <row r="46" spans="1:12" ht="13.5">
       <c r="A46" s="46"/>
@@ -16486,29 +16462,59 @@
     </row>
   </sheetData>
   <mergeCells count="93">
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="D1:I2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G18:H18"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="B11:D11"/>
@@ -16525,60 +16531,30 @@
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K16:L16"/>
     <mergeCell ref="I18:J18"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="D1:I2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
